--- a/exports/final/bom/BOM.xlsx
+++ b/exports/final/bom/BOM.xlsx
@@ -13557,12 +13557,12 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-TC-01</t>
+          <t xml:space="preserve">TH-INS-01</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+          <t xml:space="preserve">secondary thermal barrier tape for grounded hot-shield exterior</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="0">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="E156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="0">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="G156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">received product; exact backing/adhesive/rating must be recorded</t>
         </is>
       </c>
       <c r="I156" t="inlineStr" s="0">
@@ -13617,12 +13617,12 @@
       </c>
       <c r="M156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
         </is>
       </c>
       <c r="N156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/thermal/parts/TH-TC-01/drawing_notes.md</t>
+          <t xml:space="preserve">docs/drawings/v0.8/EX-003_heater_thermocouple.svg</t>
         </is>
       </c>
       <c r="O156" t="inlineStr" s="0">
@@ -13637,99 +13637,186 @@
       </c>
       <c r="Q156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=user stock; cash_class=REUSE_PENDING; status=RECEIPT_TEST_HOLD; quantity_unit=roll minimum; no safety function; no direct heater/barrel/die/cutoff/probe/terminal/vent coverage; S4 coupon smoke required; P9 adhesive-interface peak+U95+30 C must not exceed documented continuous rating; edge lift after cooldown &lt;=2 mm</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">TH-TC-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">THERMAL</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">exports/thermal/parts/TH-TC-01/drawing_notes.md</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">TH-TCR-01</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr" s="0">
+      <c r="B158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Thermocouple stop-collar retainer bridge</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr" s="0">
+      <c r="C158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr" s="0">
+      <c r="D158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">THERMAL</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr" s="0">
+      <c r="E158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr" s="0">
+      <c r="F158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">REQUIRED</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr" s="0">
+      <c r="G158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">BUY_TO_SPEC</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr" s="0">
+      <c r="H158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">304 stainless t1.5; process=buy/custom fabricate to thermal drawing note</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr" s="0">
+      <c r="I158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr" s="0">
+      <c r="J158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr" s="0">
+      <c r="K158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr" s="0">
+      <c r="L158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr" s="0">
+      <c r="M158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr" s="0">
+      <c r="N158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">exports/thermal/parts/TH-TCR-01/drawing_notes.md</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr" s="0">
+      <c r="O158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr" s="0">
+      <c r="P158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr" s="0">
+      <c r="Q158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q157"/>
+  <autoFilter ref="A1:Q158"/>
 </worksheet>
 </file>
 
@@ -22249,78 +22336,115 @@
     <row r="156">
       <c r="A156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-TC-01</t>
+          <t xml:space="preserve">TH-INS-01</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+          <t xml:space="preserve">secondary thermal barrier tape for grounded hot-shield exterior</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">received product; exact backing/adhesive/rating must be recorded</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">TH-TC-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">TH-TCR-01</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr" s="0">
+      <c r="B158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Thermocouple stop-collar retainer bridge</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr" s="0">
+      <c r="C158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr" s="0">
+      <c r="D158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">BUY_TO_SPEC</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr" s="0">
+      <c r="E158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr" s="0">
+      <c r="F158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr" s="0">
+      <c r="G158" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">304 stainless t1.5; process=buy/custom fabricate to thermal drawing note</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G157"/>
+  <autoFilter ref="A1:G158"/>
 </worksheet>
 </file>
--- a/exports/final/bom/BOM.xlsx
+++ b/exports/final/bom/BOM.xlsx
@@ -13562,7 +13562,7 @@
       </c>
       <c r="B156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">secondary thermal barrier tape for grounded hot-shield exterior</t>
+          <t xml:space="preserve">PI gold finger polyimide thermal barrier tape, 25 mm x 30 m received roll</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="0">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="H156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">received product; exact backing/adhesive/rating must be recorded</t>
+          <t xml:space="preserve">polyimide film; listing also states fluororesin release material; adhesive chemistry not specified</t>
         </is>
       </c>
       <c r="I156" t="inlineStr" s="0">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Q156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=user stock; cash_class=REUSE_PENDING; status=RECEIPT_TEST_HOLD; quantity_unit=roll minimum; no safety function; no direct heater/barrel/die/cutoff/probe/terminal/vent coverage; S4 coupon smoke required; P9 adhesive-interface peak+U95+30 C must not exceed documented continuous rating; edge lift after cooldown &lt;=2 mm</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=user stock; cash_class=REUSE_PENDING; status=RECEIPT_TEST_HOLD; quantity_unit=each; received product claim long-term 220-280 C, short-term 300 C; use conservative 220 C continuous design basis; S4/P9 interface peak+U95 &lt;=190 C; no safety function; shield exterior only</t>
         </is>
       </c>
     </row>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="B156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">secondary thermal barrier tape for grounded hot-shield exterior</t>
+          <t xml:space="preserve">PI gold finger polyimide thermal barrier tape, 25 mm x 30 m received roll</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="0">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="G156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">received product; exact backing/adhesive/rating must be recorded</t>
+          <t xml:space="preserve">polyimide film; listing also states fluororesin release material; adhesive chemistry not specified</t>
         </is>
       </c>
     </row>

--- a/exports/final/bom/BOM.xlsx
+++ b/exports/final/bom/BOM.xlsx
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I61" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">sealed flake path; feeder-to-barrel interface; drawing tolerance=Ø8 h8=7.978–8.000 x300; Ø3.00 +0.05/0 cross-holes at Z8 and Z292; lower hole matched with FD-MET-02, upper with FD-CP-01; paddle sweep Ø50/100/120 at Z183/228/273; straightness0.10; 2.2 N·m design torque SF≥2; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">sealed flake path; feeder-to-barrel interface; drawing tolerance=Ø8 h8=7.978–8.000 x300; Ø3.00 +0.05/0 cross-holes at Z11 and Z292; lower hole matched with FD-MET-02, upper with FD-CP-01; paddle sweep Ø50/100/120 at Z183/228/273; straightness0.10; 2.2 N·m design torque SF≥2; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J61" t="inlineStr" s="0">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B72" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">compact profile frame cut set</t>
+          <t xml:space="preserve">GGM R1 integrated profile cut set</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="0">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="H72" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">20x20 aluminum profile 890x4 430x10 660x6 300x2 318x1 280x2 50x1 plus local 20x40 660x2</t>
+          <t xml:space="preserve">2020: 36 members / 15078 mm; 2040: 4 members / 2180 mm; member-by-member frame_cut_list.csv</t>
         </is>
       </c>
       <c r="I72" t="inlineStr" s="0">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="N72" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/FR-001_frame.svg</t>
+          <t xml:space="preserve">exports/final/frame_v08/FRAME_CUT_AND_TIE_KO.pdf</t>
         </is>
       </c>
       <c r="O72" t="inlineStr" s="0">
@@ -6329,19 +6329,19 @@
       </c>
       <c r="Q72" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=project lab; cash_class=REUSE_PENDING; status=UNVERIFIED; quantity_unit=each; revision safety-orchestration-closure-v0.6.1; geometry unchanged from 60ccd92fe9a7df35b550a2a57649b1263da09d10; 14.668 m total; local 2040 shredder rails; exports/fabrication/frame_cut_list.csv</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=project lab; cash_class=REUSE_PENDING; status=UNVERIFIED; quantity_unit=each; GGM_FRAME_R1_REDUCED_20260912; nominal cuts before kerf/upper tolerance; actual stock unidentified; FR-TIE-01 separate; exports/final/frame_v08/FRAME_CUT_AND_TIE_KO.pdf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GD-01</t>
+          <t xml:space="preserve">FR-TIE-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">cutter and hot-zone guards</t>
+          <t xml:space="preserve">formed steel bottom frame tie replacing 2020 L430</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="0">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GUARD</t>
+          <t xml:space="preserve">FRAME</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="0">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="H73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">metal sheet plus ABS cold covers</t>
+          <t xml:space="preserve">S275JR; finished U40x20x3 R3 x470; 4xD5.5 at X10/460 Y12/28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">moving/hot hazard reach protection and service interlock</t>
+          <t xml:space="preserve">profile joint squareness and table load path</t>
         </is>
       </c>
       <c r="J73" t="inlineStr" s="0">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="N73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/GD-001_guards_panels.svg</t>
+          <t xml:space="preserve">exports/final/frame_v08/FR-TIE-01.svg</t>
         </is>
       </c>
       <c r="O73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 18; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 2; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">hardware safety function; firmware monitoring only; never sole protection</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=lot; reach and fragment coupon pending</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=project-lab metal fabrication; cash_class=MAKE; status=DESIGNED_PHYSICAL_HOLD; quantity_unit=each; FR-TIE-01.step / FRAME_CUT_AND_TIE_KO.pdf; four M5x10 class8.8 with washer OD&lt;=10 and compatible T-nut; received torque/engagement and P2 approval required</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_ChainGuard</t>
+          <t xml:space="preserve">GD-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_ChainGuard</t>
+          <t xml:space="preserve">cutter and hot-zone guards</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="0">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DRIVE</t>
+          <t xml:space="preserve">GUARD</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="0">
@@ -6453,27 +6453,27 @@
       </c>
       <c r="G74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1mm folded steel plus2x20x20 mounting tabs; twoM3 to front bearing plate; interlock required; process=1 mm 강판 절단/절곡 + 두 mounting tab</t>
+          <t xml:space="preserve">metal sheet plus ABS cold covers</t>
         </is>
       </c>
       <c r="I74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">기본 outer118 x24 x173, t1.0; 아래 전개 설명과 좌표 cutout을 따른다. STEP은 완성 외형.; 20 x10 x2 foot +20 x20 x2 upright tab2개를 용접. tab holeD3.40, front bearing plate에 M3x0.5.; 전면 개구는 두 bearing판의 실물 외곽으로 막혀야 한다. panel/plate gap0.30 nominal, 파편·손 접근 경로 확인.; 절곡 반경1.0, 각도90 +/-1deg. flat blank는 실제 절곡장비의 bend allowance로 계산; 외곽치수는 완성치수.; 전면 mounting2개 외 service cover 잠금과 NC interlock은 전기 안전회로에 연결. 현장 무단 제거 금지.; GGM delta: 기본 outer118 x24 x173, t1.0; 아래 전개 설명과 좌표 cutout을 따른다. STEP은 완성 외형.; 20 x10 x2 foot +20 x20 x2 upright tab2개를 용접. tab holeD3.40, front bearing plate에 M3x0.5.; 전면 개구는 두 bearing판의 실물 외곽으로 막혀야 한다. panel/plate gap0.30 nominal, 파편·손 접근 경로 확인.; 절곡 반경1.0, 각도90 +/-1deg. flat blank는 실제 절곡장비의 bend allowance로 계산; 외곽치수는 완성치수.; 전면 mounting2개 외 service cover 잠금과 NC interlock은 전기 안전회로에 연결. 현장 무단 제거 금지.</t>
+          <t xml:space="preserve">moving/hot hazard reach protection and service interlock</t>
         </is>
       </c>
       <c r="J74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE_CUSTOM</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—deviation requires drive-interface review</t>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="0">
@@ -6483,39 +6483,39 @@
       </c>
       <c r="M74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="N74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf; exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf</t>
+          <t xml:space="preserve">docs/drawings/v0.8/GD-001_guards_panels.svg</t>
         </is>
       </c>
       <c r="O74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 8; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 18; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM/BTS7960 released profile; commissioning calibration remains NOT_RUN</t>
+          <t xml:space="preserve">hardware safety function; firmware monitoring only; never sole protection</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv; GGM drive delta drawing bound by drive_ggm manifest</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=lot; reach and fragment coupon pending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_CouplingGuard</t>
+          <t xml:space="preserve">GGM_ChainGuard</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_CouplingGuard</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_ChainGuard</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="0">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="H75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=1 mm 강판 롤 + 2 mm half flange</t>
+          <t xml:space="preserve">1mm folded steel plus2x20x20 mounting tabs; twoM3 to front bearing plate; interlock required; process=1 mm 강판 절단/절곡 + 두 mounting tab</t>
         </is>
       </c>
       <c r="I75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">shell OD50/ID48, 길이58.00 +/-0.30. R2에서 실제 t1에 맞춰 재료 표기를 정정.; 상하2개 half-cover, seam gap1.00 +/-0.20. front flange OD76/ID48 x2, 각 half에2개 M3 clearance.; 장착4개 좌표는 조립도 참조. flange와 shell은 연속 접합 후 버 제거. 통전 전 service interlock 실물 확인.; GGM delta: shell OD50/ID48, 길이58.00 +/-0.30. R2에서 실제 t1에 맞춰 재료 표기를 정정.; 상하2개 half-cover, seam gap1.00 +/-0.20. front flange OD76/ID48 x2, 각 half에2개 M3 clearance.; 장착4개 좌표는 조립도 참조. flange와 shell은 연속 접합 후 버 제거. 통전 전 service interlock 실물 확인.</t>
+          <t xml:space="preserve">기본 outer118 x24 x173, t1.0; 아래 전개 설명과 좌표 cutout을 따른다. STEP은 완성 외형.; 20 x10 x2 foot +20 x20 x2 upright tab2개를 용접. tab holeD3.40, front bearing plate에 M3x0.5.; 전면 개구는 두 bearing판의 실물 외곽으로 막혀야 한다. panel/plate gap0.30 nominal, 파편·손 접근 경로 확인.; 절곡 반경1.0, 각도90 +/-1deg. flat blank는 실제 절곡장비의 bend allowance로 계산; 외곽치수는 완성치수.; 전면 mounting2개 외 service cover 잠금과 NC interlock은 전기 안전회로에 연결. 현장 무단 제거 금지.; GGM delta: 기본 outer118 x24 x173, t1.0; 아래 전개 설명과 좌표 cutout을 따른다. STEP은 완성 외형.; 20 x10 x2 foot +20 x20 x2 upright tab2개를 용접. tab holeD3.40, front bearing plate에 M3x0.5.; 전면 개구는 두 bearing판의 실물 외곽으로 막혀야 한다. panel/plate gap0.30 nominal, 파편·손 접근 경로 확인.; 절곡 반경1.0, 각도90 +/-1deg. flat blank는 실제 절곡장비의 bend allowance로 계산; 외곽치수는 완성치수.; 전면 mounting2개 외 service cover 잠금과 NC interlock은 전기 안전회로에 연결. 현장 무단 제거 금지.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr" s="0">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="O75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 12; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 8; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P75" t="inlineStr" s="0">
@@ -6597,12 +6597,12 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_FuseInput</t>
+          <t xml:space="preserve">GGM_EX_CouplingGuard</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseInput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_CouplingGuard</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="0">
@@ -6632,12 +6632,12 @@
       </c>
       <c r="H76" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
+          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=1 mm 강판 롤 + 2 mm half flange</t>
         </is>
       </c>
       <c r="I76" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.; GGM delta: S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.</t>
+          <t xml:space="preserve">shell OD50/ID48, 길이58.00 +/-0.30. R2에서 실제 t1에 맞춰 재료 표기를 정정.; 상하2개 half-cover, seam gap1.00 +/-0.20. front flange OD76/ID48 x2, 각 half에2개 M3 clearance.; 장착4개 좌표는 조립도 참조. flange와 shell은 연속 접합 후 버 제거. 통전 전 service interlock 실물 확인.; GGM delta: shell OD50/ID48, 길이58.00 +/-0.30. R2에서 실제 t1에 맞춰 재료 표기를 정정.; 상하2개 half-cover, seam gap1.00 +/-0.20. front flange OD76/ID48 x2, 각 half에2개 M3 clearance.; 장착4개 좌표는 조립도 참조. flange와 shell은 연속 접합 후 버 제거. 통전 전 service interlock 실물 확인.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr" s="0">
@@ -6684,12 +6684,12 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_FuseOutput</t>
+          <t xml:space="preserve">GGM_EX_FuseInput</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseOutput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseInput</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="0">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="I77" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.; GGM delta: S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.</t>
+          <t xml:space="preserve">S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.; GGM delta: S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr" s="0">
@@ -6771,12 +6771,12 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_FusePinBlank</t>
+          <t xml:space="preserve">GGM_EX_FuseOutput</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FusePinBlank</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseOutput</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="0">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="H78" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
         </is>
       </c>
       <c r="I78" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.; GGM delta: 이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.</t>
+          <t xml:space="preserve">S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.; GGM delta: S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr" s="0">
@@ -6858,12 +6858,12 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_MotorKey</t>
+          <t xml:space="preserve">GGM_EX_FusePinBlank</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_MotorKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FusePinBlank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="0">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="H79" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
         </is>
       </c>
       <c r="I79" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
+          <t xml:space="preserve">이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.; GGM delta: 이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr" s="0">
@@ -6945,12 +6945,12 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_Mount</t>
+          <t xml:space="preserve">GGM_EX_MotorKey</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_Mount</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_MotorKey</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="0">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="H80" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm S275 plate; use catalog eccentric output datum; process=판재 절단 + 드릴</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
       <c r="I80" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275 t6.00 +/-0.10. 120 x140 외곽 +/-0.20.; D36.50 +0.10/0, 4xD6.60 PCD104. 출력축 중심과 bolt-grid 중심은18.00 mm 다름.; 하부 2xD5.50 관통은 rail 체결. 도면 좌표를 따르고 기어박스 사각 중앙을 축으로 삼지 않는다.; A=모터 접촉면, B=출력축, C=바닥 모서리. 접촉면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.; GGM delta: S275 t6.00 +/-0.10. 120 x140 외곽 +/-0.20.; D36.50 +0.10/0, 4xD6.60 PCD104. 출력축 중심과 bolt-grid 중심은18.00 mm 다름.; 하부 2xD5.50 관통은 rail 체결. 도면 좌표를 따르고 기어박스 사각 중앙을 축으로 삼지 않는다.; A=모터 접촉면, B=출력축, C=바닥 모서리. 접촉면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.</t>
+          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr" s="0">
@@ -7032,12 +7032,12 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_RadialCap</t>
+          <t xml:space="preserve">GGM_EX_Mount</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialCap</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_Mount</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="0">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="H81" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel t2; ID27.4 outer-ring-only retainer; M3 screws; process=2 mm 판재 절단 + 드릴</t>
+          <t xml:space="preserve">6 mm S275 plate; use catalog eccentric output datum; process=판재 절단 + 드릴</t>
         </is>
       </c>
       <c r="I81" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">R2 변경: ID18에서 ID27.40 +0.10/0으로 수정. OD46.00 +/-0.10, t2.00 +/-0.05.; 2xD3.40 관통 PCD40. M3x10와 washer. 외륜만 유지하며 씰/내륜 접촉 금지.; 캡과 홀더의 선택 shim으로 axial endplay0.05~0.20. 강제로 조여 bearing을 pre-load하지 않는다.; GGM delta: R2 변경: ID18에서 ID27.40 +0.10/0으로 수정. OD46.00 +/-0.10, t2.00 +/-0.05.; 2xD3.40 관통 PCD40. M3x10와 washer. 외륜만 유지하며 씰/내륜 접촉 금지.; 캡과 홀더의 선택 shim으로 axial endplay0.05~0.20. 강제로 조여 bearing을 pre-load하지 않는다.</t>
+          <t xml:space="preserve">S275 t6.00 +/-0.10. 120 x140 외곽 +/-0.20.; D36.50 +0.10/0, 4xD6.60 PCD104. 출력축 중심과 bolt-grid 중심은18.00 mm 다름.; 하부 2xD5.50 관통은 rail 체결. 도면 좌표를 따르고 기어박스 사각 중앙을 축으로 삼지 않는다.; A=모터 접촉면, B=출력축, C=바닥 모서리. 접촉면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.; GGM delta: S275 t6.00 +/-0.10. 120 x140 외곽 +/-0.20.; D36.50 +0.10/0, 4xD6.60 PCD104. 출력축 중심과 bolt-grid 중심은18.00 mm 다름.; 하부 2xD5.50 관통은 rail 체결. 도면 좌표를 따르고 기어박스 사각 중앙을 축으로 삼지 않는다.; A=모터 접촉면, B=출력축, C=바닥 모서리. 접촉면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr" s="0">
@@ -7119,12 +7119,12 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_RadialHolder</t>
+          <t xml:space="preserve">GGM_EX_RadialCap</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialHolder</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialCap</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="0">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="H82" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275 t10; bore32.03; 4x4.5; matching M4 in thrust plate; process=판재 보링/리머 + 드릴/탭</t>
+          <t xml:space="preserve">steel t2; ID27.4 outer-ring-only retainer; M3 screws; process=2 mm 판재 절단 + 드릴</t>
         </is>
       </c>
       <c r="I82" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275 48 x48 x10.00 +/-0.05. 중심 D32.030 +/-0.010, Ra1.6.; 4xD4.50 관통, 38 x38 정사각. thrust plate의 대응 4개 M4x0.7과 결합.; 2xD2.50은 M3x0.5 캡용 관통탭, 유효6 mm 이상. 홀더 보어는 screw와 추력좌면 기준으로 정렬.; 베어링 정면을 압출 추력 전달면으로 사용하지 않는다. 지정된51102 경로를 유지.; GGM delta: S275 48 x48 x10.00 +/-0.05. 중심 D32.030 +/-0.010, Ra1.6.; 4xD4.50 관통, 38 x38 정사각. thrust plate의 대응 4개 M4x0.7과 결합.; 2xD2.50은 M3x0.5 캡용 관통탭, 유효6 mm 이상. 홀더 보어는 screw와 추력좌면 기준으로 정렬.; 베어링 정면을 압출 추력 전달면으로 사용하지 않는다. 지정된51102 경로를 유지.</t>
+          <t xml:space="preserve">R2 변경: ID18에서 ID27.40 +0.10/0으로 수정. OD46.00 +/-0.10, t2.00 +/-0.05.; 2xD3.40 관통 PCD40. M3x10와 washer. 외륜만 유지하며 씰/내륜 접촉 금지.; 캡과 홀더의 선택 shim으로 axial endplay0.05~0.20. 강제로 조여 bearing을 pre-load하지 않는다.; GGM delta: R2 변경: ID18에서 ID27.40 +0.10/0으로 수정. OD46.00 +/-0.10, t2.00 +/-0.05.; 2xD3.40 관통 PCD40. M3x10와 washer. 외륜만 유지하며 씰/내륜 접촉 금지.; 캡과 홀더의 선택 shim으로 axial endplay0.05~0.20. 강제로 조여 bearing을 pre-load하지 않는다.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr" s="0">
@@ -7206,12 +7206,12 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_ScrewKey</t>
+          <t xml:space="preserve">GGM_EX_RadialHolder</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_ScrewKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialHolder</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="0">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H83" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S275 t10; bore32.03; 4x4.5; matching M4 in thrust plate; process=판재 보링/리머 + 드릴/탭</t>
         </is>
       </c>
       <c r="I83" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
+          <t xml:space="preserve">S275 48 x48 x10.00 +/-0.05. 중심 D32.030 +/-0.010, Ra1.6.; 4xD4.50 관통, 38 x38 정사각. thrust plate의 대응 4개 M4x0.7과 결합.; 2xD2.50은 M3x0.5 캡용 관통탭, 유효6 mm 이상. 홀더 보어는 screw와 추력좌면 기준으로 정렬.; 베어링 정면을 압출 추력 전달면으로 사용하지 않는다. 지정된51102 경로를 유지.; GGM delta: S275 48 x48 x10.00 +/-0.05. 중심 D32.030 +/-0.010, Ra1.6.; 4xD4.50 관통, 38 x38 정사각. thrust plate의 대응 4개 M4x0.7과 결합.; 2xD2.50은 M3x0.5 캡용 관통탭, 유효6 mm 이상. 홀더 보어는 screw와 추력좌면 기준으로 정렬.; 베어링 정면을 압출 추력 전달면으로 사용하지 않는다. 지정된51102 경로를 유지.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr" s="0">
@@ -7293,12 +7293,12 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_front</t>
+          <t xml:space="preserve">GGM_EX_ScrewKey</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_front</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_ScrewKey</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="0">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="H84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel ID12.1 OD17 shim/spacer; inner ring only; process=강관/washer 선삭</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
       <c r="I84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">모두 OD17.00 -0.05/0, ID12.10 +0.03/0. 길이는 대응 부품표2.60/2.00/3.00/1.00 mm.; 길이 +/-0.02, 양 끝면 평행도0.02, Ra1.6. 외륜/씰이 아닌 내륜만 누른다.; 최종 collar와 shim은 두 bearing 사이 강제 예압 없이 축방향 유격0.05~0.20에서 선택.; GGM delta: 모두 OD17.00 -0.05/0, ID12.10 +0.03/0. 길이는 대응 부품표2.60/2.00/3.00/1.00 mm.; 길이 +/-0.02, 양 끝면 평행도0.02, Ra1.6. 외륜/씰이 아닌 내륜만 누른다.; 최종 collar와 shim은 두 bearing 사이 강제 예압 없이 축방향 유격0.05~0.20에서 선택.</t>
+          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr" s="0">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="O84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 7; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 12; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P84" t="inlineStr" s="0">
@@ -7380,12 +7380,12 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_pinionfront</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_front</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionfront</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_front</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="0">
@@ -7467,12 +7467,12 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_pinionrear</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_pinionfront</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionrear</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionfront</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="0">
@@ -7554,12 +7554,12 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_rear</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_pinionrear</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_rear</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionrear</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="0">
@@ -7641,12 +7641,12 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_12T</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_rear</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ANSI #35 12T steel keyed sprocket</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_rear</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="0">
@@ -7671,27 +7671,27 @@
       </c>
       <c r="G88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY #35 12T steel, hub15, key4.1; GGM_SH_Jackshaft D12 h6; 4x4 steel; key flank carries torque</t>
+          <t xml:space="preserve">steel ID12.1 OD17 shim/spacer; inner ring only; process=강관/washer 선삭</t>
         </is>
       </c>
       <c r="I88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">keyed torque path; radial TIR &lt;= 0.10 mm; assembled axial shift+U95 &lt;= 0.20 mm; chain alignment &lt;= 0.20/150 mm; received maker axial retention required</t>
+          <t xml:space="preserve">모두 OD17.00 -0.05/0, ID12.10 +0.03/0. 길이는 대응 부품표2.60/2.00/3.00/1.00 mm.; 길이 +/-0.02, 양 끝면 평행도0.02, Ra1.6. 외륜/씰이 아닌 내륜만 누른다.; 최종 collar와 shim은 두 bearing 사이 강제 예압 없이 축방향 유격0.05~0.20에서 선택.; GGM delta: 모두 OD17.00 -0.05/0, ID12.10 +0.03/0. 길이는 대응 부품표2.60/2.00/3.00/1.00 mm.; 길이 +/-0.02, 양 끝면 평행도0.02, Ra1.6. 외륜/씰이 아닌 내륜만 누른다.; 최종 collar와 shim은 두 bearing 사이 강제 예압 없이 축방향 유격0.05~0.20에서 선택.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—received keyed #35 sprocket must pass P1/P4 fit and retention evidence</t>
+          <t xml:space="preserve">NOT_APPLICABLE_CUSTOM</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—failed bore/key/retention/TIR requires an engineering adapter revision</t>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires drive-interface review</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="0">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="M88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CHECK_EXISTING_STOCK_FIRST—PURCHASE_USER_APPROVAL_REQUIRED—PHYSICAL_RECEIPT_HOLD</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
         </is>
       </c>
       <c r="N88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/SH-004_chain_phase_gear.svg</t>
+          <t xml:space="preserve">exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf; exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf</t>
         </is>
       </c>
       <c r="O88" t="inlineStr" s="0">
@@ -7716,24 +7716,24 @@
       </c>
       <c r="P88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM torque/current protection calibration; sprocket retention is mechanical</t>
+          <t xml:space="preserve">GGM/BTS7960 released profile; commissioning calibration remains NOT_RUN</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CURRENT GGM PURCHASED SPROCKET SOURCE: control/ggm_drive_contract.json + analysis/drive_acceptance_v08/drive_component_register.csv; key carries torque; maker retention hardware is axial-only; DRV-02 is superseded</t>
+          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv; GGM drive delta drawing bound by drive_ggm manifest</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_30T</t>
+          <t xml:space="preserve">GGM_SH_12T</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ANSI #35 30T steel keyed sprocket</t>
+          <t xml:space="preserve">ANSI #35 12T steel keyed sprocket</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="0">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="H89" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY #35 30T steel, hub28, key6.1; CUT-05R D25 h6 drive-end land; 6x6x20 steel; key flank carries torque</t>
+          <t xml:space="preserve">BUY #35 12T steel, hub15, key4.1; GGM_SH_Jackshaft D12 h6; 4x4 steel; key flank carries torque</t>
         </is>
       </c>
       <c r="I89" t="inlineStr" s="0">
@@ -7815,12 +7815,12 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Angle201</t>
+          <t xml:space="preserve">GGM_SH_30T</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle201</t>
+          <t xml:space="preserve">ANSI #35 30T steel keyed sprocket</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="0">
@@ -7845,27 +7845,27 @@
       </c>
       <c r="G90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE</t>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
         </is>
       </c>
       <c r="H90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275 stock angle; continuous3mm fillet both legs; jig before welding; process=6 mm 판재 두 조각 + 용접</t>
+          <t xml:space="preserve">BUY #35 30T steel, hub28, key6.1; CUT-05R D25 h6 drive-end land; 6x6x20 steel; key flank carries torque</t>
         </is>
       </c>
       <c r="I90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">각 22 x36 x6 foot와22 x100 x6 web. 조립 높이106.00 +/-0.20.; 재고 angle을 잘라도 동일한 두께/외형/접촉면이 필요. 모터판과 바닥판에3 mm 연속 필릿, 비드 간섭 제거.; 용접 jig 상태에서 축 위치 확인. 냉각 후 평면도0.15 및 수직도0.10/100 확인.; GGM delta: 각 22 x36 x6 foot와22 x100 x6 web. 조립 높이106.00 +/-0.20.; 재고 angle을 잘라도 동일한 두께/외형/접촉면이 필요. 모터판과 바닥판에3 mm 연속 필릿, 비드 간섭 제거.; 용접 jig 상태에서 축 위치 확인. 냉각 후 평면도0.15 및 수직도0.10/100 확인.</t>
+          <t xml:space="preserve">keyed torque path; radial TIR &lt;= 0.10 mm; assembled axial shift+U95 &lt;= 0.20 mm; chain alignment &lt;= 0.20/150 mm; received maker axial retention required</t>
         </is>
       </c>
       <c r="J90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE_CUSTOM</t>
+          <t xml:space="preserve">NONE_APPROVED—received keyed #35 sprocket must pass P1/P4 fit and retention evidence</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—deviation requires drive-interface review</t>
+          <t xml:space="preserve">NONE_APPROVED—failed bore/key/retention/TIR requires an engineering adapter revision</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="0">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="M90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
+          <t xml:space="preserve">CHECK_EXISTING_STOCK_FIRST—PURCHASE_USER_APPROVAL_REQUIRED—PHYSICAL_RECEIPT_HOLD</t>
         </is>
       </c>
       <c r="N90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf; exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf</t>
+          <t xml:space="preserve">docs/drawings/v0.8/SH-004_chain_phase_gear.svg</t>
         </is>
       </c>
       <c r="O90" t="inlineStr" s="0">
@@ -7890,24 +7890,24 @@
       </c>
       <c r="P90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM/BTS7960 released profile; commissioning calibration remains NOT_RUN</t>
+          <t xml:space="preserve">GGM torque/current protection calibration; sprocket retention is mechanical</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv; GGM drive delta drawing bound by drive_ggm manifest</t>
+          <t xml:space="preserve">CURRENT GGM PURCHASED SPROCKET SOURCE: control/ggm_drive_contract.json + analysis/drive_acceptance_v08/drive_component_register.csv; key carries torque; maker retention hardware is axial-only; DRV-02 is superseded</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Angle83</t>
+          <t xml:space="preserve">GGM_SH_Angle201</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle83</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle201</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="0">
@@ -7989,12 +7989,12 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Base</t>
+          <t xml:space="preserve">GGM_SH_Angle83</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Base</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle83</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="0">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="H92" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm S275 sheet; fourM6 base holes plus fourM5 end-tap post holes; process=판재 절단 + 드릴</t>
+          <t xml:space="preserve">S275 stock angle; continuous3mm fillet both legs; jig before welding; process=6 mm 판재 두 조각 + 용접</t>
         </is>
       </c>
       <c r="I92" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275, 235 x 253 x 6.00 mm. 두께 6.00 +/-0.10; 외곽 +/-0.20.; 상면 A, X 최소 모서리 B, Y 최소 모서리 C. 구멍 위치는 좌표표 기준 +/-0.10.; 4xD6.60 +0.10/0: M6 관통. 4xD5.50 +0.10/0: profile 끝단 M5 체결용.; 지지면 평면도 0.15, 버 제거 C0.2. 가공 후 두 rail 위 흔들림 확인.; GGM delta: S275, 235 x 253 x 6.00 mm. 두께 6.00 +/-0.10; 외곽 +/-0.20.; 상면 A, X 최소 모서리 B, Y 최소 모서리 C. 구멍 위치는 좌표표 기준 +/-0.10.; 4xD6.60 +0.10/0: M6 관통. 4xD5.50 +0.10/0: profile 끝단 M5 체결용.; 지지면 평면도 0.15, 버 제거 C0.2. 가공 후 두 rail 위 흔들림 확인.</t>
+          <t xml:space="preserve">각 22 x36 x6 foot와22 x100 x6 web. 조립 높이106.00 +/-0.20.; 재고 angle을 잘라도 동일한 두께/외형/접촉면이 필요. 모터판과 바닥판에3 mm 연속 필릿, 비드 간섭 제거.; 용접 jig 상태에서 축 위치 확인. 냉각 후 평면도0.15 및 수직도0.10/100 확인.; GGM delta: 각 22 x36 x6 foot와22 x100 x6 web. 조립 높이106.00 +/-0.20.; 재고 angle을 잘라도 동일한 두께/외형/접촉면이 필요. 모터판과 바닥판에3 mm 연속 필릿, 비드 간섭 제거.; 용접 jig 상태에서 축 위치 확인. 냉각 후 평면도0.15 및 수직도0.10/100 확인.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr" s="0">
@@ -8076,12 +8076,12 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap271</t>
+          <t xml:space="preserve">GGM_SH_Base</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap271</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Base</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="0">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="H93" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2 mm steel; M3 retainer screws; process=2 mm 판재 절단 + 드릴</t>
+          <t xml:space="preserve">6 mm S275 sheet; fourM6 base holes plus fourM5 end-tap post holes; process=판재 절단 + 드릴</t>
         </is>
       </c>
       <c r="I93" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">OD46.00 +/-0.10, ID27.40 +0.10/0, t2.00 +/-0.05. 2xD3.40 관통, PCD40.; 외륜에만 접촉. 씰/내륜과 간섭하지 않는지 수령 bearing으로 확인.; M3x10 class8.8와 washer; 유효물림6 mm 이상, 바닥 여유1 mm 이상. 외륜 endplay0.05~0.20을 shim으로 맞춘다.; GGM delta: OD46.00 +/-0.10, ID27.40 +0.10/0, t2.00 +/-0.05. 2xD3.40 관통, PCD40.; 외륜에만 접촉. 씰/내륜과 간섭하지 않는지 수령 bearing으로 확인.; M3x10 class8.8와 washer; 유효물림6 mm 이상, 바닥 여유1 mm 이상. 외륜 endplay0.05~0.20을 shim으로 맞춘다.</t>
+          <t xml:space="preserve">S275, 235 x 253 x 6.00 mm. 두께 6.00 +/-0.10; 외곽 +/-0.20.; 상면 A, X 최소 모서리 B, Y 최소 모서리 C. 구멍 위치는 좌표표 기준 +/-0.10.; 4xD6.60 +0.10/0: M6 관통. 4xD5.50 +0.10/0: profile 끝단 M5 체결용.; 지지면 평면도 0.15, 버 제거 C0.2. 가공 후 두 rail 위 흔들림 확인.; GGM delta: S275, 235 x 253 x 6.00 mm. 두께 6.00 +/-0.10; 외곽 +/-0.20.; 상면 A, X 최소 모서리 B, Y 최소 모서리 C. 구멍 위치는 좌표표 기준 +/-0.10.; 4xD6.60 +0.10/0: M6 관통. 4xD5.50 +0.10/0: profile 끝단 M5 체결용.; 지지면 평면도 0.15, 버 제거 C0.2. 가공 후 두 rail 위 흔들림 확인.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr" s="0">
@@ -8163,12 +8163,12 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap283</t>
+          <t xml:space="preserve">GGM_SH_BearingCap271</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap283</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap271</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="0">
@@ -8250,12 +8250,12 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap301</t>
+          <t xml:space="preserve">GGM_SH_BearingCap283</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap301</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap283</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="0">
@@ -8337,12 +8337,12 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap313</t>
+          <t xml:space="preserve">GGM_SH_BearingCap301</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap313</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap301</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="0">
@@ -8424,12 +8424,12 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingPlate273</t>
+          <t xml:space="preserve">GGM_SH_BearingCap313</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate273</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap313</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="0">
@@ -8459,12 +8459,12 @@
       </c>
       <c r="H97" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">216x60x10 plate,32.03 bore,193x40 asymmetric hole grid; rings retained by caps; process=판재 + 보링/리머 + 탭</t>
+          <t xml:space="preserve">2 mm steel; M3 retainer screws; process=2 mm 판재 절단 + 드릴</t>
         </is>
       </c>
       <c r="I97" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.; R2 front판에만 chain guard tab용2xM3x0.5를 좌표표대로 추가한다.; GGM delta: S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.; R2 front판에만 chain guard tab용2xM3x0.5를 좌표표대로 추가한다.</t>
+          <t xml:space="preserve">OD46.00 +/-0.10, ID27.40 +0.10/0, t2.00 +/-0.05. 2xD3.40 관통, PCD40.; 외륜에만 접촉. 씰/내륜과 간섭하지 않는지 수령 bearing으로 확인.; M3x10 class8.8와 washer; 유효물림6 mm 이상, 바닥 여유1 mm 이상. 외륜 endplay0.05~0.20을 shim으로 맞춘다.; GGM delta: OD46.00 +/-0.10, ID27.40 +0.10/0, t2.00 +/-0.05. 2xD3.40 관통, PCD40.; 외륜에만 접촉. 씰/내륜과 간섭하지 않는지 수령 bearing으로 확인.; M3x10 class8.8와 washer; 유효물림6 mm 이상, 바닥 여유1 mm 이상. 외륜 endplay0.05~0.20을 shim으로 맞춘다.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr" s="0">
@@ -8511,12 +8511,12 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingPlate303</t>
+          <t xml:space="preserve">GGM_SH_BearingPlate273</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate303</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate273</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="0">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="I98" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.; GGM delta: S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.</t>
+          <t xml:space="preserve">S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.; R2 front판에만 chain guard tab용2xM3x0.5를 좌표표대로 추가한다.; GGM delta: S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.; R2 front판에만 chain guard tab용2xM3x0.5를 좌표표대로 추가한다.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr" s="0">
@@ -8598,12 +8598,12 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_CouplingGuard</t>
+          <t xml:space="preserve">GGM_SH_BearingPlate303</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CouplingGuard</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate303</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="0">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="H99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=2 mm 강판 롤 + 분할 seam</t>
+          <t xml:space="preserve">216x60x10 plate,32.03 bore,193x40 asymmetric hole grid; rings retained by caps; process=판재 + 보링/리머 + 탭</t>
         </is>
       </c>
       <c r="I99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">shell OD54/ID50 x57.00 +/-0.30; steel t2.0, 상하2개 half-cover.; seam gap1.00 +/-0.20, front flangeOD76/ID50 x2.0. flange4개 D3.40 mounting.; 장착판 대응4개M3x0.5. captiveM3x8 기준; 실제물림/끝면여유 확인. flange용접 후 중심 정렬.; 커플링과 최소 radial gap1.0 확인. 실제 NC service interlock은 별도 수령·설계검증 후 연결.; GGM delta: shell OD54/ID50 x57.00 +/-0.30; steel t2.0, 상하2개 half-cover.; seam gap1.00 +/-0.20, front flangeOD76/ID50 x2.0. flange4개 D3.40 mounting.; 장착판 대응4개M3x0.5. captiveM3x8 기준; 실제물림/끝면여유 확인. flange용접 후 중심 정렬.; 커플링과 최소 radial gap1.0 확인. 실제 NC service interlock은 별도 수령·설계검증 후 연결.</t>
+          <t xml:space="preserve">S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.; GGM delta: S275, 216 x60 x10.00 +/-0.05. D32.030 +/-0.010; bore Ra1.6 이하.; 193 x40 hole grid는 축에 대하여 비대칭이다. 좌표표로 가공. 4xD5.50 관통.; 2xD2.50은 M3x0.5 탭드릴 표기. 양면에서 유효 나사6 mm 이상; 캡용 2개 관통탭.; 두 판은 동일 jig로 보링. 합성 축심차0.03 이하 목표; 외륜 endplay는 선택 shim으로0.05~0.20.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr" s="0">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="O99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 8; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 7; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P99" t="inlineStr" s="0">
@@ -8685,12 +8685,12 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_CutterKey</t>
+          <t xml:space="preserve">GGM_SH_CouplingGuard</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CutterKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CouplingGuard</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="0">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="H100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6x6x20 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=2 mm 강판 롤 + 분할 seam</t>
         </is>
       </c>
       <c r="I100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
+          <t xml:space="preserve">shell OD54/ID50 x57.00 +/-0.30; steel t2.0, 상하2개 half-cover.; seam gap1.00 +/-0.20, front flangeOD76/ID50 x2.0. flange4개 D3.40 mounting.; 장착판 대응4개M3x0.5. captiveM3x8 기준; 실제물림/끝면여유 확인. flange용접 후 중심 정렬.; 커플링과 최소 radial gap1.0 확인. 실제 NC service interlock은 별도 수령·설계검증 후 연결.; GGM delta: shell OD54/ID50 x57.00 +/-0.30; steel t2.0, 상하2개 half-cover.; seam gap1.00 +/-0.20, front flangeOD76/ID50 x2.0. flange4개 D3.40 mounting.; 장착판 대응4개M3x0.5. captiveM3x8 기준; 실제물림/끝면여유 확인. flange용접 후 중심 정렬.; 커플링과 최소 radial gap1.0 확인. 실제 NC service interlock은 별도 수령·설계검증 후 연결.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr" s="0">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="O100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 7; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 8; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P100" t="inlineStr" s="0">
@@ -8772,12 +8772,12 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_FuseInput</t>
+          <t xml:space="preserve">GGM_SH_CutterKey</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseInput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CutterKey</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="0">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="H101" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
+          <t xml:space="preserve">6x6x20 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
       <c r="I101" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.; GGM delta: S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.</t>
+          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="0">
@@ -8859,12 +8859,12 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_FuseOutput</t>
+          <t xml:space="preserve">GGM_SH_FuseInput</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseOutput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseInput</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="0">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="I102" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.; GGM delta: S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.</t>
+          <t xml:space="preserve">S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.; GGM delta: S45C. 축방향 원점 Z0=입력 끝면, A=축 보어. Z0~22 OD28; Z22~26 OD46; Z26~30 OD20.; 보어 D12.050 +0.010/0 관통; 키홈 폭4.10 +0.03/0, 중심에서 홈 천장8.025. 외경/보어 TIR0.03.; 정합 pilot OD20.000 -0.020/0, Ra1.6. 정합부 축방향면 직각도0.03.; 전단핀 hole D3.10 +0.02/0, R16.00 +/-0.03. Z22부터 flange 관통; 출력허브와 조립 jig에서 match-drill.; Z12의 radial D3.30은 M4x0.7 탭드릴; 유효나사5 mm 이상. set screw는 축방향 유지, 토크는 키로 전달.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="0">
@@ -8946,12 +8946,12 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_FusePinBlank</t>
+          <t xml:space="preserve">GGM_SH_FuseOutput</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FusePinBlank</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseOutput</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="0">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="H103" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
         </is>
       </c>
       <c r="I103" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.; GGM delta: 이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.</t>
+          <t xml:space="preserve">S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.; GGM delta: S45C. 공통 결합 datum Z26.40~30.40 OD46, Z30.40~52.40 OD28; 전장26.00 +/-0.05.; 보어 D12.050 +0.010/0, key4.10 +0.03/0. 입력면 counterbore D20.100 +0.020/0, 깊이4.20 +/-0.05.; 전단핀 D3.10 +0.02/0, R16.00 +/-0.03. 입력허브와 match-drill. 양 flange 사이 축간극0.40 +/-0.10.; 공통 datum Z40.40 radial D3.30은 M4x0.7, 유효나사5 mm 이상. 외경/보어 TIR0.03.; 핀 파단 뒤 pilot이 걸리지 않도록 무하중 자유회전 확인. 이 구조는 압력 방출장치가 아니다.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="0">
@@ -9033,12 +9033,12 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_JackInputKey</t>
+          <t xml:space="preserve">GGM_SH_FusePinBlank</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackInputKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FusePinBlank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="0">
@@ -9068,12 +9068,12 @@
       </c>
       <c r="H104" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
         </is>
       </c>
       <c r="I104" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
+          <t xml:space="preserve">이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.; GGM delta: 이 도면은 교정용 blank이며 운전용 전단핀 완성도가 아니다. 황동 lot를 구분한다.; 몸통 D3.00 -0.02/0 x11.70, 머리 D4.00 x1.00, 총12.70 +/-0.05.; 공통 coupling datum: 머리 Z20.70~21.70, 몸통21.70~33.40. 유지용 교차공 D0.90, 중심 Z32.00.; R16 단일 전단 가정에서 목경 약2.416~2.483 mm는 계산 참고값만 해당. 목경을 확정값으로 가공 발주하지 않는다.; 설계검증 종료와 별도 시험 승인 뒤, 실제 결합 coupon의 8.8~9.3 N.m 해제 결과로 목경/길이를 확정한다.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="0">
@@ -9120,12 +9120,12 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_JackSprocketKey</t>
+          <t xml:space="preserve">GGM_SH_JackInputKey</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackSprocketKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackInputKey</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="0">
@@ -9207,12 +9207,12 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Jackshaft</t>
+          <t xml:space="preserve">GGM_SH_JackSprocketKey</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Jackshaft</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackSprocketKey</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="0">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="H106" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C 12 h6 x78; two 4 mm keys; process=규격 S45C 봉 + 선삭 + 키홈</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
       <c r="I106" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C 공급 상태는 상온 항복강도300 MPa 이상 근거 필요. 전장78.00 +/-0.10.; D12 h6=11.989~12.000. 베어링 land Ra0.8 이하, 기타 원통 Ra1.6 이하.; 축 원점=전방 끝면. 키홈1 Z2.40~24.40; 키홈2 Z39.00~57.00. 폭4.00 +0.02/0; 바닥은 축중심에서3.50 mm.; 베어링 land Z27~37 및57~67은 원통면을 보존. 끝면 C0.2, 키홈 뿌리 R0.2 이하.; 두 land 기준 TIR0.03 이하. h6는 현재 원형 설계 기준이며 수령 bearing과 실제 fit/creep 판정 전 운전 금지.; GGM delta: S45C 공급 상태는 상온 항복강도300 MPa 이상 근거 필요. 전장78.00 +/-0.10.; D12 h6=11.989~12.000. 베어링 land Ra0.8 이하, 기타 원통 Ra1.6 이하.; 축 원점=전방 끝면. 키홈1 Z2.40~24.40; 키홈2 Z39.00~57.00. 폭4.00 +0.02/0; 바닥은 축중심에서3.50 mm.; 베어링 land Z27~37 및57~67은 원통면을 보존. 끝면 C0.2, 키홈 뿌리 R0.2 이하.; 두 land 기준 TIR0.03 이하. h6는 현재 원형 설계 기준이며 수령 bearing과 실제 fit/creep 판정 전 운전 금지.</t>
+          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="0">
@@ -9294,12 +9294,12 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_MotorKey</t>
+          <t xml:space="preserve">GGM_SH_Jackshaft</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_MotorKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Jackshaft</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="0">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="H107" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S45C 12 h6 x78; two 4 mm keys; process=규격 S45C 봉 + 선삭 + 키홈</t>
         </is>
       </c>
       <c r="I107" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
+          <t xml:space="preserve">S45C 공급 상태는 상온 항복강도300 MPa 이상 근거 필요. 전장78.00 +/-0.10.; D12 h6=11.989~12.000. 베어링 land Ra0.8 이하, 기타 원통 Ra1.6 이하.; 축 원점=전방 끝면. 키홈1 Z2.40~24.40; 키홈2 Z39.00~57.00. 폭4.00 +0.02/0; 바닥은 축중심에서3.50 mm.; 베어링 land Z27~37 및57~67은 원통면을 보존. 끝면 C0.2, 키홈 뿌리 R0.2 이하.; 두 land 기준 TIR0.03 이하. h6는 현재 원형 설계 기준이며 수령 bearing과 실제 fit/creep 판정 전 운전 금지.; GGM delta: S45C 공급 상태는 상온 항복강도300 MPa 이상 근거 필요. 전장78.00 +/-0.10.; D12 h6=11.989~12.000. 베어링 land Ra0.8 이하, 기타 원통 Ra1.6 이하.; 축 원점=전방 끝면. 키홈1 Z2.40~24.40; 키홈2 Z39.00~57.00. 폭4.00 +0.02/0; 바닥은 축중심에서3.50 mm.; 베어링 land Z27~37 및57~67은 원통면을 보존. 끝면 C0.2, 키홈 뿌리 R0.2 이하.; 두 land 기준 TIR0.03 이하. h6는 현재 원형 설계 기준이며 수령 bearing과 실제 fit/creep 판정 전 운전 금지.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="0">
@@ -9381,12 +9381,12 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Mount</t>
+          <t xml:space="preserve">GGM_SH_MotorKey</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Mount</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_MotorKey</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="0">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="H108" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm S275 plate; 4x6.6 PCD104; pilot36.5; process=판재 절단 + 드릴 + 지그 용접</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
       <c r="I108" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275 t6.00 +/-0.10. 140 x 190.167, 외곽 +/-0.20.; D36.50 +0.10/0 통과공은 정밀 파일럿이 아니다. 축 정렬은 조립 검사로 확보.; 4xD6.60 +0.10/0, PCD104 중심은 출력축에서 18.00 mm 편심. 표를 따라 가공.; M6 관통 볼트 사용. 두 보강 angle을 jig에서 3 mm 연속 필릿 용접. 용접 뒤 정렬면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.; GGM delta: S275 t6.00 +/-0.10. 140 x 190.167, 외곽 +/-0.20.; D36.50 +0.10/0 통과공은 정밀 파일럿이 아니다. 축 정렬은 조립 검사로 확보.; 4xD6.60 +0.10/0, PCD104 중심은 출력축에서 18.00 mm 편심. 표를 따라 가공.; M6 관통 볼트 사용. 두 보강 angle을 jig에서 3 mm 연속 필릿 용접. 용접 뒤 정렬면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.</t>
+          <t xml:space="preserve">4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.; GGM delta: 4x4: 길이25(2개),22(1),15(1),17(1). 6x6: 길이20(1개). 표의 bbox는 회전 배치 크기일 수 있다.; 4 mm 폭3.985~4.000, 6 mm 폭5.985~6.000; 높이는 nominal-0.03/0, 길이-0.20/0.; 키홈 천장과 키 상면0.10 이상 여유. 버 제거 C0.1, 억지 타격 금지. 실제 flank contact와 손회전 확인.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="0">
@@ -9468,12 +9468,12 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_220_100</t>
+          <t xml:space="preserve">GGM_SH_Mount</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_100</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Mount</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="0">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="H109" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel spacer 12/6.6 x10; process=규격 강관 절단 + 끝면 다듬기</t>
+          <t xml:space="preserve">6 mm S275 plate; 4x6.6 PCD104; pilot36.5; process=판재 절단 + 드릴 + 지그 용접</t>
         </is>
       </c>
       <c r="I109" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">OD12.00 +/-0.10, ID6.60 +0.10/0, nominal L10.00 +/-0.05.; 체인 장력은4개를 동일 길이8~13 mm로 조절. 같은 set의 길이 차이0.03 이하.; 서로 다른 spacer 높이로 축 기울기를 만들지 않는다. 연질 출력 spacer 금지.; GGM delta: OD12.00 +/-0.10, ID6.60 +0.10/0, nominal L10.00 +/-0.05.; 체인 장력은4개를 동일 길이8~13 mm로 조절. 같은 set의 길이 차이0.03 이하.; 서로 다른 spacer 높이로 축 기울기를 만들지 않는다. 연질 출력 spacer 금지.</t>
+          <t xml:space="preserve">S275 t6.00 +/-0.10. 140 x 190.167, 외곽 +/-0.20.; D36.50 +0.10/0 통과공은 정밀 파일럿이 아니다. 축 정렬은 조립 검사로 확보.; 4xD6.60 +0.10/0, PCD104 중심은 출력축에서 18.00 mm 편심. 표를 따라 가공.; M6 관통 볼트 사용. 두 보강 angle을 jig에서 3 mm 연속 필릿 용접. 용접 뒤 정렬면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.; GGM delta: S275 t6.00 +/-0.10. 140 x 190.167, 외곽 +/-0.20.; D36.50 +0.10/0 통과공은 정밀 파일럿이 아니다. 축 정렬은 조립 검사로 확보.; 4xD6.60 +0.10/0, PCD104 중심은 출력축에서 18.00 mm 편심. 표를 따라 가공.; M6 관통 볼트 사용. 두 보강 angle을 jig에서 3 mm 연속 필릿 용접. 용접 뒤 정렬면 평면도0.15.; R2: coupling cover 4xD2.50은 M3x0.5 관통탭, 유효5 mm 이상. 나사 끝단 돌출/모터 간섭 금지.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="0">
@@ -9555,12 +9555,12 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_220_280</t>
+          <t xml:space="preserve">GGM_SH_Spacer_220_100</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_280</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_100</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="0">
@@ -9642,12 +9642,12 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_90_100</t>
+          <t xml:space="preserve">GGM_SH_Spacer_220_280</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_100</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_280</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="0">
@@ -9729,12 +9729,12 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_90_280</t>
+          <t xml:space="preserve">GGM_SH_Spacer_90_100</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_280</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_100</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="0">
@@ -9816,12 +9816,12 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">HP-01</t>
+          <t xml:space="preserve">GGM_SH_Spacer_90_280</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">refillable sliding-lid hopper</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_280</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="0">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">HOPPER</t>
+          <t xml:space="preserve">DRIVE</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="0">
@@ -9846,27 +9846,27 @@
       </c>
       <c r="G113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">MAKE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IN-HOP-01 plus PPR-C01/C02</t>
+          <t xml:space="preserve">steel spacer 12/6.6 x10; process=규격 강관 절단 + 끝면 다듬기</t>
         </is>
       </c>
       <c r="I113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">anti-reach opening and removable hopper interface</t>
+          <t xml:space="preserve">OD12.00 +/-0.10, ID6.60 +0.10/0, nominal L10.00 +/-0.05.; 체인 장력은4개를 동일 길이8~13 mm로 조절. 같은 set의 길이 차이0.03 이하.; 서로 다른 spacer 높이로 축 기울기를 만들지 않는다. 연질 출력 spacer 금지.; GGM delta: OD12.00 +/-0.10, ID6.60 +0.10/0, nominal L10.00 +/-0.05.; 체인 장력은4개를 동일 길이8~13 mm로 조절. 같은 set의 길이 차이0.03 이하.; 서로 다른 spacer 높이로 축 기울기를 만들지 않는다. 연질 출력 spacer 금지.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+          <t xml:space="preserve">NOT_APPLICABLE_CUSTOM</t>
         </is>
       </c>
       <c r="K113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires drive-interface review</t>
         </is>
       </c>
       <c r="L113" t="inlineStr" s="0">
@@ -9876,39 +9876,39 @@
       </c>
       <c r="M113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
         </is>
       </c>
       <c r="N113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/FD-001_hopper.svg</t>
+          <t xml:space="preserve">exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf; exports/final/manufacturing/drive_ggm/PPR_GGM_MANUFACTURING_DRAWINGS_r2.pdf</t>
         </is>
       </c>
       <c r="O113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 9; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 7; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">GGM/BTS7960 released profile; commissioning calibration remains NOT_RUN</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=each; 4.5 L usable; fabrication STEP/DXF/note under exports/fabrication</t>
+          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv; GGM drive delta drawing bound by drive_ggm manifest</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IN-HOP-01</t>
+          <t xml:space="preserve">HP-01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Refillable input hopper</t>
+          <t xml:space="preserve">refillable sliding-lid hopper</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="0">
@@ -9933,22 +9933,22 @@
       </c>
       <c r="G114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2 mm 5052-H32 aluminum; process=roll cone/cylinder + TIG weld + deburr</t>
+          <t xml:space="preserve">IN-HOP-01 plus PPR-C01/C02</t>
         </is>
       </c>
       <c r="I114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">anti-reach opening and removable hopper interface; drawing tolerance=OD200 x straight150 + cone60; outlet Ø40; wall 2.0; lid rail datum flatness 0.5; leak-free dry-flake seams; datum=A=material-flow axis; B=mounting face; C=drive/sensor centre plane; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">anti-reach opening and removable hopper interface</t>
         </is>
       </c>
       <c r="J114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K114" t="inlineStr" s="0">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="M114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="N114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/IN-HOP-01.pdf</t>
+          <t xml:space="preserve">docs/drawings/v0.8/FD-001_hopper.svg</t>
         </is>
       </c>
       <c r="O114" t="inlineStr" s="0">
@@ -9983,19 +9983,19 @@
       </c>
       <c r="Q114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=each; 4.5 L usable; fabrication STEP/DXF/note under exports/fabrication</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PL-01</t>
+          <t xml:space="preserve">IN-HOP-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">puller pair with tach</t>
+          <t xml:space="preserve">Refillable input hopper</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="0">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="D115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PULLER</t>
+          <t xml:space="preserve">HOPPER</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="0">
@@ -10020,22 +10020,22 @@
       </c>
       <c r="G115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="H115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">FM-PL-01/RL-01/AX-01 plus donor motor and tach</t>
+          <t xml:space="preserve">2 mm 5052-H32 aluminum; process=roll cone/cylinder + TIG weld + deburr</t>
         </is>
       </c>
       <c r="I115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">roller alignment, pinch guard and tach calibration</t>
+          <t xml:space="preserve">anti-reach opening and removable hopper interface; drawing tolerance=OD200 x straight150 + cone60; outlet Ø40; wall 2.0; lid rail datum flatness 0.5; leak-free dry-flake seams; datum=A=material-flow axis; B=mounting face; C=drive/sensor centre plane; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
         </is>
       </c>
       <c r="K115" t="inlineStr" s="0">
@@ -10045,44 +10045,44 @@
       </c>
       <c r="L115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">UNVERIFIED—label, rating, shaft, condition and functional test required</t>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="M115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_INVENTORY_VERIFICATION_REQUIRED</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="N115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/FM-002_gauge_puller.svg</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/IN-HOP-01.pdf</t>
         </is>
       </c>
       <c r="O115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 16; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 9; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=UNVERIFIED; quantity_unit=each; closed inner speed PI; roller diameter and pulses/rev require CRC calibration; matched plates/rollers and metal spindles</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C01</t>
+          <t xml:space="preserve">PL-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Sliding hopper lid</t>
+          <t xml:space="preserve">puller pair with tach</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="0">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3D_PRINT</t>
+          <t xml:space="preserve">PULLER</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="0">
@@ -10107,22 +10107,22 @@
       </c>
       <c r="G116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_3D_PRINT</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 20% infill</t>
+          <t xml:space="preserve">FM-PL-01/RL-01/AX-01 plus donor motor and tach</t>
         </is>
       </c>
       <c r="I116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal hopper rails and lid-interlock flag; tolerance=0.35 mm slide</t>
+          <t xml:space="preserve">roller alignment, pinch guard and tach calibration</t>
         </is>
       </c>
       <c r="J116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K116" t="inlineStr" s="0">
@@ -10132,44 +10132,44 @@
       </c>
       <c r="L116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE</t>
+          <t xml:space="preserve">UNVERIFIED—label, rating, shaft, condition and functional test required</t>
         </is>
       </c>
       <c r="M116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PRINT_PACKAGE_PASS</t>
+          <t xml:space="preserve">USER_INVENTORY_VERIFICATION_REQUIRED</t>
         </is>
       </c>
       <c r="N116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C01/dimension_sheet.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/FM-002_gauge_puller.svg</t>
         </is>
       </c>
       <c r="O116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 9; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 16; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/print/print_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=UNVERIFIED; quantity_unit=each; closed inner speed PI; roller diameter and pulses/rev require CRC calibration; matched plates/rollers and metal spindles</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C02</t>
+          <t xml:space="preserve">PPR-C01</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Anti-reach baffle chute</t>
+          <t xml:space="preserve">Sliding hopper lid</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="0">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="H117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 25% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 20% infill</t>
         </is>
       </c>
       <c r="I117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=hopper and metal cutter chamber; tolerance=0.40 mm flake path</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal hopper rails and lid-interlock flag; tolerance=finished latch hole Ø4.50–4.70; screw head flush or recessed≤0.05; rail slide gap0.35</t>
         </is>
       </c>
       <c r="J117" t="inlineStr" s="0">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="N117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C02/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C01/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O117" t="inlineStr" s="0">
@@ -10251,12 +10251,12 @@
     <row r="118">
       <c r="A118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C03</t>
+          <t xml:space="preserve">PPR-C02</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Flake bin sheet corner</t>
+          <t xml:space="preserve">Anti-reach baffle chute</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="0">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="E118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="0">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="H118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.28 mm; 4 walls; 25% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 25% infill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=1 mm sheet bin and screen rails; tolerance=0.30 mm sheet slot</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=hopper and metal cutter chamber; tolerance=0.40 mm flake path</t>
         </is>
       </c>
       <c r="J118" t="inlineStr" s="0">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="N118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C03/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C02/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 10; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 9; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P118" t="inlineStr" s="0">
@@ -10338,12 +10338,12 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C04</t>
+          <t xml:space="preserve">PPR-C03</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Screen drawer handle</t>
+          <t xml:space="preserve">Flake bin sheet corner</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="0">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="E119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="0">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="H119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 35% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.28 mm; 4 walls; 25% infill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal screen; tolerance=0.25 mm</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=1.00 ±0.05 mm sheet bin and screen rails; tolerance=sheet slot 1.40 ±0.30 mm</t>
         </is>
       </c>
       <c r="J119" t="inlineStr" s="0">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="N119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C04/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C03/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 9; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 10; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P119" t="inlineStr" s="0">
@@ -10425,12 +10425,12 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C05</t>
+          <t xml:space="preserve">PPR-C04</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Cooling duct segment</t>
+          <t xml:space="preserve">Screen drawer handle</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="0">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="E120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="0">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="H120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 15% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 35% infill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=80 mm fan and next duct; tolerance=0.30 mm flange registration</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal screen; tolerance=0.25 mm</t>
         </is>
       </c>
       <c r="J120" t="inlineStr" s="0">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="N120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C05/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C04/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 14; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 9; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P120" t="inlineStr" s="0">
@@ -10512,12 +10512,12 @@
     <row r="121">
       <c r="A121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C06</t>
+          <t xml:space="preserve">PPR-C05</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Gauge enclosure half</t>
+          <t xml:space="preserve">Cooling duct segment</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="0">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="H121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 25% infill</t>
+          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 15% infill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=LED/photodiode cross frame and opposite half; tolerance=0.20 mm optical slit</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=80 mm fan and next duct; tolerance=0.30 mm flange registration</t>
         </is>
       </c>
       <c r="J121" t="inlineStr" s="0">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="N121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C06/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C05/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 15; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 14; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P121" t="inlineStr" s="0">
@@ -10599,12 +10599,12 @@
     <row r="122">
       <c r="A122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C07</t>
+          <t xml:space="preserve">PPR-C06</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Puller pinch guard</t>
+          <t xml:space="preserve">Gauge enclosure</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="0">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="E122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="0">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="H122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 20% infill</t>
+          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 25% infill</t>
         </is>
       </c>
       <c r="I122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal puller plate; tolerance=0.40 mm guard gap</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=LED/photodiode cross frame; tolerance=finished holes Ø3.40–3.50; 0.20 mm optical slit; install X/Y pair on one straight Ø1.75 calibration wire, match-drill mounting datum, scan both axes and accept optical centreline offset &lt;=0.10 mm</t>
         </is>
       </c>
       <c r="J122" t="inlineStr" s="0">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="N122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C07/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C06/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 16; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 15; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P122" t="inlineStr" s="0">
@@ -10686,12 +10686,12 @@
     <row r="123">
       <c r="A123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C08</t>
+          <t xml:space="preserve">PPR-C07</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Solid-strand guide axle bracket</t>
+          <t xml:space="preserve">Puller pinch guard</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="0">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="E123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="0">
@@ -10721,12 +10721,12 @@
       </c>
       <c r="H123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
+          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 20% infill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=FM-GA-01 fixed Ø5 axle and profile; 625 bearings are seated in FM-GR-01; tolerance=Ø5.2 +0.20/0 printed/reamed axle clearance</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal puller plate; tolerance=0.40 mm guard gap</t>
         </is>
       </c>
       <c r="J123" t="inlineStr" s="0">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="N123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C08/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C07/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 16; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P123" t="inlineStr" s="0">
@@ -10773,12 +10773,12 @@
     <row r="124">
       <c r="A124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C09</t>
+          <t xml:space="preserve">PPR-C08</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool cone adapter</t>
+          <t xml:space="preserve">Solid-strand guide axle bracket</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="0">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="H124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 35% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=12 mm metal spindle and metal collar; tolerance=0.30 mm spool core</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=FM-GA-01 fixed Ø5 axle and profile; 625 bearings are seated in FM-GR-01; tolerance=finished bore Ø5.20–5.40; align both loose T-slot brackets on the same axle before 2.0 N.m torque; axle shall pass by hand without visible bending</t>
         </is>
       </c>
       <c r="J124" t="inlineStr" s="0">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="N124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C09/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C08/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O124" t="inlineStr" s="0">
@@ -10860,12 +10860,12 @@
     <row r="125">
       <c r="A125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C10</t>
+          <t xml:space="preserve">PPR-C09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Traverse carriage</t>
+          <t xml:space="preserve">Spool cone adapter</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="0">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="E125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="0">
@@ -10895,12 +10895,12 @@
       </c>
       <c r="H125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 35% infill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=donor rods and GT2 belt; tolerance=0.20 mm after ream</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=12 mm metal spindle, metal collar, and received spool; tolerance=finished spindle bore Ø12.20–12.40; diametral clearance0.20–0.411 to Ø12 h6; cone-to-received-spool contact is separately selected</t>
         </is>
       </c>
       <c r="J125" t="inlineStr" s="0">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="N125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C10/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C09/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O125" t="inlineStr" s="0">
@@ -10947,12 +10947,12 @@
     <row r="126">
       <c r="A126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C11</t>
+          <t xml:space="preserve">PPR-C10</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Control panel bezel</t>
+          <t xml:space="preserve">Traverse carriage</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="0">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 20% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal control panel; tolerance=0.25 mm TFT</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=specified Ø8 h6 rods and GT2 belt; tolerance=finished rod bores Ø8.40–8.50; finished clamp holes Ø4.50–4.70; use two Ø8 h6=7.991–8.000 ground steel rods</t>
         </is>
       </c>
       <c r="J126" t="inlineStr" s="0">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="N126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C11/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C10/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 22; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P126" t="inlineStr" s="0">
@@ -11034,12 +11034,12 @@
     <row r="127">
       <c r="A127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C12</t>
+          <t xml:space="preserve">PPR-C11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Cable duct clamp</t>
+          <t xml:space="preserve">Control panel bezel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="0">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="E127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="0">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="H127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 50% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 20% infill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=20 mm profile and fixed 18x18 cable duct; tolerance=18.6 mm cavity; 0.30 mm/side</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=metal control panel; tolerance=finished holes Ø3.40–3.50; 0.25 mm TFT</t>
         </is>
       </c>
       <c r="J127" t="inlineStr" s="0">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="N127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/print/PPR-C12/dimension_sheet.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C11/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 20; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 22; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P127" t="inlineStr" s="0">
@@ -11121,12 +11121,12 @@
     <row r="128">
       <c r="A128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-EXTRUDER-ASM</t>
+          <t xml:space="preserve">PPR-C12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-EXTRUDER-ASM</t>
+          <t xml:space="preserve">Cable duct clamp</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="0">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="D128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CAD_REFERENCE</t>
+          <t xml:space="preserve">3D_PRINT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="0">
@@ -11151,47 +11151,47 @@
       </c>
       <c r="G128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">REFERENCE_ONLY</t>
+          <t xml:space="preserve">MAKE_3D_PRINT</t>
         </is>
       </c>
       <c r="H128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">not separately procured; canonical BOM item or assembly</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 50% infill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference identity must resolve to canonical BOM/drawing</t>
+          <t xml:space="preserve">printed interface per dimension sheet; no structural hot/high-load path; mating=20 mm profile and fixed 18x18 cable duct; tolerance=18.6 mm cavity; 0.30 mm/side</t>
         </is>
       </c>
       <c r="J128" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">NOT_APPLICABLE</t>
-        </is>
-      </c>
       <c r="M128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE_REFERENCE</t>
+          <t xml:space="preserve">PRINT_PACKAGE_PASS</t>
         </is>
       </c>
       <c r="N128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/EX-001_extruder_assembly.svg</t>
+          <t xml:space="preserve">exports/print/PPR-C12/dimension_sheet.svg</t>
         </is>
       </c>
       <c r="O128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 11; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 20; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P128" t="inlineStr" s="0">
@@ -11201,19 +11201,19 @@
       </c>
       <c r="Q128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">active_part_set reference; canonical=PPR-EXTRUDER-ASM; exclude from procurement roll-up</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/print/print_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FEEDER-ASM</t>
+          <t xml:space="preserve">PPR-EXTRUDER-ASM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FEEDER-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-EXTRUDER-ASM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="0">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="N129" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/FD-003_positive_feeder.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/EX-001_extruder_assembly.svg</t>
         </is>
       </c>
       <c r="O129" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 10; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 11; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P129" t="inlineStr" s="0">
@@ -11288,19 +11288,19 @@
       </c>
       <c r="Q129" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">active_part_set reference; canonical=PPR-FEEDER-ASM; exclude from procurement roll-up</t>
+          <t xml:space="preserve">active_part_set reference; canonical=PPR-EXTRUDER-ASM; exclude from procurement roll-up</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FORMING-ASM</t>
+          <t xml:space="preserve">PPR-FEEDER-ASM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FORMING-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FEEDER-ASM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="0">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="N130" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/FM-001_cooling_strand_path.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/FD-003_positive_feeder.svg</t>
         </is>
       </c>
       <c r="O130" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 14; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 10; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P130" t="inlineStr" s="0">
@@ -11375,19 +11375,19 @@
       </c>
       <c r="Q130" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">active_part_set reference; canonical=PPR-FORMING-ASM; exclude from procurement roll-up</t>
+          <t xml:space="preserve">active_part_set reference; canonical=PPR-FEEDER-ASM; exclude from procurement roll-up</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FRAME-ASM</t>
+          <t xml:space="preserve">PPR-FORMING-ASM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FRAME-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FORMING-ASM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="0">
@@ -11447,12 +11447,12 @@
       </c>
       <c r="N131" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/FR-001_frame.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/FM-001_cooling_strand_path.svg</t>
         </is>
       </c>
       <c r="O131" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 2; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 14; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P131" t="inlineStr" s="0">
@@ -11462,19 +11462,19 @@
       </c>
       <c r="Q131" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">active_part_set reference; canonical=PPR-FRAME-ASM; exclude from procurement roll-up</t>
+          <t xml:space="preserve">active_part_set reference; canonical=PPR-FORMING-ASM; exclude from procurement roll-up</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FULL-ASM</t>
+          <t xml:space="preserve">PPR-FRAME-ASM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FULL-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FRAME-ASM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="0">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="N132" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/ASM-001_full_assembly.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/FR-001_frame.svg</t>
         </is>
       </c>
       <c r="O132" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 1; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 2; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P132" t="inlineStr" s="0">
@@ -11549,19 +11549,19 @@
       </c>
       <c r="Q132" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">active_part_set reference; canonical=PPR-FULL-ASM; exclude from procurement roll-up</t>
+          <t xml:space="preserve">active_part_set reference; canonical=PPR-FRAME-ASM; exclude from procurement roll-up</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-SHREDDER-ASM</t>
+          <t xml:space="preserve">PPR-FULL-ASM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-SHREDDER-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FULL-ASM</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="0">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="N133" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/SH-001_shredder_assembly.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/ASM-001_full_assembly.svg</t>
         </is>
       </c>
       <c r="O133" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 4; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 1; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P133" t="inlineStr" s="0">
@@ -11636,19 +11636,19 @@
       </c>
       <c r="Q133" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">active_part_set reference; canonical=PPR-SHREDDER-ASM; exclude from procurement roll-up</t>
+          <t xml:space="preserve">active_part_set reference; canonical=PPR-FULL-ASM; exclude from procurement roll-up</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SF-01</t>
+          <t xml:space="preserve">PPR-SHREDDER-ASM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">latching E-stop and hardwired cut</t>
+          <t xml:space="preserve">reference alias: PPR-SHREDDER-ASM</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="0">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="D134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SAFETY</t>
+          <t xml:space="preserve">CAD_REFERENCE</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="0">
@@ -11673,27 +11673,27 @@
       </c>
       <c r="G134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">REFERENCE_ONLY</t>
         </is>
       </c>
       <c r="H134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">qualified switch plus relay topology</t>
+          <t xml:space="preserve">not separately procured; canonical BOM item or assembly</t>
         </is>
       </c>
       <c r="I134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">hardwired E-stop/interlock/thermal chain independent of firmware</t>
+          <t xml:space="preserve">reference identity must resolve to canonical BOM/drawing</t>
         </is>
       </c>
       <c r="J134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="K134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="L134" t="inlineStr" s="0">
@@ -11703,39 +11703,39 @@
       </c>
       <c r="M134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
+          <t xml:space="preserve">NOT_APPLICABLE_REFERENCE</t>
         </is>
       </c>
       <c r="N134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/EL-001_electrical_enclosure.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/SH-001_shredder_assembly.svg</t>
         </is>
       </c>
       <c r="O134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 21; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 4; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">hardware safety function; firmware monitoring only; never sole protection</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=stock/buy; cash_class=MIXED; status=PHYSICAL_GATE; quantity_unit=each; software independent</t>
+          <t xml:space="preserve">active_part_set reference; canonical=PPR-SHREDDER-ASM; exclude from procurement roll-up</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SF-02</t>
+          <t xml:space="preserve">SF-01</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">lid and service interlocks</t>
+          <t xml:space="preserve">latching E-stop and hardwired cut</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="0">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="E135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="0">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="H135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">positive opening switch candidate</t>
+          <t xml:space="preserve">qualified switch plus relay topology</t>
         </is>
       </c>
       <c r="I135" t="inlineStr" s="0">
@@ -11810,19 +11810,19 @@
       </c>
       <c r="Q135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=stock/buy; cash_class=MIXED; status=PHYSICAL_GATE; quantity_unit=each; hardware branch inhibit</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=stock/buy; cash_class=MIXED; status=PHYSICAL_GATE; quantity_unit=each; software independent</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SF-03</t>
+          <t xml:space="preserve">SF-02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">thermal and branch fuses</t>
+          <t xml:space="preserve">lid and service interlocks</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="0">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="E136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="0">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="H136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">temperature/current rated</t>
+          <t xml:space="preserve">positive opening switch candidate</t>
         </is>
       </c>
       <c r="I136" t="inlineStr" s="0">
@@ -11897,19 +11897,19 @@
       </c>
       <c r="Q136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=stock/buy; cash_class=MIXED; status=PHYSICAL_GATE; quantity_unit=lot; not optional; TH-FUSE-01 quantity 3 = TF-BARREL + TF-DIE installed in series in K0 coil chain + one same-spec spare; F-H1..F-H4 are separate 5 A branch overcurrent fuses; exact MPN/rating per thermal cutoff contract and heater RFQ receipt gate</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=stock/buy; cash_class=MIXED; status=PHYSICAL_GATE; quantity_unit=each; hardware branch inhibit</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-01</t>
+          <t xml:space="preserve">SF-03</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">dual-shaft hook cutter assembly</t>
+          <t xml:space="preserve">thermal and branch fuses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="0">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="D137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SHREDDER</t>
+          <t xml:space="preserve">SAFETY</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="0">
@@ -11934,22 +11934,22 @@
       </c>
       <c r="G137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_CNC</t>
+          <t xml:space="preserve">BUY</t>
         </is>
       </c>
       <c r="H137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel</t>
+          <t xml:space="preserve">temperature/current rated</t>
         </is>
       </c>
       <c r="I137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">guarded cutter torque path and service lockout</t>
+          <t xml:space="preserve">hardwired E-stop/interlock/thermal chain independent of firmware</t>
         </is>
       </c>
       <c r="J137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE—build to released specification</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K137" t="inlineStr" s="0">
@@ -11969,34 +11969,34 @@
       </c>
       <c r="N137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/SH-001_shredder_assembly.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/EL-001_electrical_enclosure.svg</t>
         </is>
       </c>
       <c r="O137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 8; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 21; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+          <t xml:space="preserve">hardware safety function; firmware monitoring only; never sole protection</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=CNC; cash_class=CASH; status=COUPON_HOLD; quantity_unit=each; common PLA/PET path</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=stock/buy; cash_class=MIXED; status=PHYSICAL_GATE; quantity_unit=lot; not optional; TH-FUSE-01 quantity 3 = TF-BARREL + TF-DIE installed in series in K0 coil chain + one same-spec spare; F-H1..F-H4 are separate 5 A branch overcurrent fuses; exact MPN/rating per thermal cutoff contract and heater RFQ receipt gate</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-02</t>
+          <t xml:space="preserve">SH-01</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">removable 5 mm screen</t>
+          <t xml:space="preserve">dual-shaft hook cutter assembly</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="0">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="H138" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">stainless steel</t>
+          <t xml:space="preserve">steel</t>
         </is>
       </c>
       <c r="I138" t="inlineStr" s="0">
@@ -12071,19 +12071,19 @@
       </c>
       <c r="Q138" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=CNC; cash_class=CASH; status=COUPON_HOLD; quantity_unit=each; metal shim clearance</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=CNC; cash_class=CASH; status=COUPON_HOLD; quantity_unit=each; common PLA/PET path</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-03</t>
+          <t xml:space="preserve">SH-02</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">interchangeable shredder geared DC drive</t>
+          <t xml:space="preserve">removable 5 mm screen</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="0">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="G139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MAKE_CNC</t>
         </is>
       </c>
       <c r="H139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM K9DG60N2 24V + K9G75C + GGM drive r2 support/jackshaft; existing #35 12T:30T</t>
+          <t xml:space="preserve">stainless steel</t>
         </is>
       </c>
       <c r="I139" t="inlineStr" s="0">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="J139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+          <t xml:space="preserve">NOT_APPLICABLE—build to released specification</t>
         </is>
       </c>
       <c r="K139" t="inlineStr" s="0">
@@ -12158,19 +12158,19 @@
       </c>
       <c r="Q139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=buy + project-lab fabrication; cash_class=MIXED; status=SELECTED_PURCHASE_HOLD; quantity_unit=each; selected shredder drive; gearbox output 40 rpm, cutter ~16 rpm through 2.5:1 chain; digital load path covers 19.6 N.m available and 8.0 N.m software gearbox limit; receipt/alignment/pin/current physical checks NOT_RUN</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=CNC; cash_class=CASH; status=COUPON_HOLD; quantity_unit=each; metal shim clearance</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-04</t>
+          <t xml:space="preserve">SH-03</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">interchangeable chain and phase drive</t>
+          <t xml:space="preserve">interchangeable shredder geared DC drive</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="0">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="G140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">BUY</t>
         </is>
       </c>
       <c r="H140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">direct-keyed GGM_SH_12T/GGM_SH_30T #35 sprockets + DRV-03/03R phase pair + GGM 12 mm jackshaft chain path</t>
+          <t xml:space="preserve">GGM K9DG60N2 24V + K9G75C + GGM drive r2 support/jackshaft; existing #35 12T:30T</t>
         </is>
       </c>
       <c r="I140" t="inlineStr" s="0">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="M140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
+          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
         </is>
       </c>
       <c r="N140" t="inlineStr" s="0">
@@ -12245,19 +12245,19 @@
       </c>
       <c r="Q140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=each; GGM_SH_12T uses 4x4 key on jackshaft and GGM_SH_30T uses 6x6 key directly on CUT-05R; keys carry torque while received maker retention hardware is axial-only and receipt-gated; radial TIR &lt;=0.10 mm, chain alignment &lt;=0.20/150 mm, axial shift+U95 &lt;=0.20 mm; DRV-02 superseded; GGM mechanical protection target 8.8-9.3 N.m at gearbox-side coupling</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=buy + project-lab fabrication; cash_class=MIXED; status=SELECTED_PURCHASE_HOLD; quantity_unit=each; selected shredder drive; gearbox output 40 rpm, cutter ~16 rpm through 2.5:1 chain; digital load path covers 19.6 N.m available and 8.0 N.m software gearbox limit; receipt/alignment/pin/current physical checks NOT_RUN</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-05</t>
+          <t xml:space="preserve">SH-04</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">bidirectional motor driver/current feedback</t>
+          <t xml:space="preserve">interchangeable chain and phase drive</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="0">
@@ -12282,12 +12282,12 @@
       </c>
       <c r="G141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">VERIFY_REUSE_OR_BUY</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">owned BTS7960 module + external motor-lead current sensor</t>
+          <t xml:space="preserve">direct-keyed GGM_SH_12T/GGM_SH_30T #35 sprockets + DRV-03/03R phase pair + GGM 12 mm jackshaft chain path</t>
         </is>
       </c>
       <c r="I141" t="inlineStr" s="0">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="L141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">UNVERIFIED—label, rating, shaft, condition and functional test required</t>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="M141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="N141" t="inlineStr" s="0">
@@ -12332,19 +12332,19 @@
       </c>
       <c r="Q141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=project lab + sensor stock-check/buy; cash_class=MIXED; status=REUSE_CONFIRMED_SENSOR_HOLD; quantity_unit=each; BTS7960 qty1 of owned qty2 allocated to shredder; D5 RPWM/D4 LPWM/D32 enable; 6 A software overcurrent and 8.0 N.m calibrated gearbox torque limit; current sensor/calibration NOT_RUN</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=each; GGM_SH_12T uses 4x4 key on jackshaft and GGM_SH_30T uses 6x6 key directly on CUT-05R; keys carry torque while received maker retention hardware is axial-only and receipt-gated; radial TIR &lt;=0.10 mm, chain alignment &lt;=0.20/150 mm, axial shift+U95 &lt;=0.20 mm; DRV-02 superseded; GGM mechanical protection target 8.8-9.3 N.m at gearbox-side coupling</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">SH-05</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">dancer traverse spooler</t>
+          <t xml:space="preserve">bidirectional motor driver/current feedback</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="0">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="D142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SPOOLER</t>
+          <t xml:space="preserve">SHREDDER</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="0">
@@ -12369,17 +12369,17 @@
       </c>
       <c r="G142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">VERIFY_REUSE_OR_BUY</t>
         </is>
       </c>
       <c r="H142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">FM-GR/GA SP-DA/AX/RL/SH plus donor motion tach left/right limits and PPR-C08..10</t>
+          <t xml:space="preserve">owned BTS7960 module + external motor-lead current sensor</t>
         </is>
       </c>
       <c r="I142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope</t>
+          <t xml:space="preserve">guarded cutter torque path and service lockout</t>
         </is>
       </c>
       <c r="J142" t="inlineStr" s="0">
@@ -12394,22 +12394,22 @@
       </c>
       <c r="L142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE</t>
+          <t xml:space="preserve">UNVERIFIED—label, rating, shaft, condition and functional test required</t>
         </is>
       </c>
       <c r="M142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
+          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
         </is>
       </c>
       <c r="N142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/SP-001_spooler_traverse.svg</t>
+          <t xml:space="preserve">docs/drawings/v0.8/SH-001_shredder_assembly.svg</t>
         </is>
       </c>
       <c r="O142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 8; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P142" t="inlineStr" s="0">
@@ -12419,19 +12419,19 @@
       </c>
       <c r="Q142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=each; 1 kg spool; A15 spool tach and A5/A6 limits; radius remains geometry/wound-length estimate with uncertainty</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=project lab + sensor stock-check/buy; cash_class=MIXED; status=REUSE_CONFIRMED_SENSOR_HOLD; quantity_unit=each; BTS7960 qty1 of owned qty2 allocated to shredder; D5 RPWM/D4 LPWM/D32 enable; 6 A software overcurrent and 8.0 N.m calibrated gearbox torque limit; current sensor/calibration NOT_RUN</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-AX-01</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer pivot/roller axles</t>
+          <t xml:space="preserve">dancer traverse spooler</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="0">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="E143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="0">
@@ -12456,22 +12456,22 @@
       </c>
       <c r="G143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Ø8 h6 stainless shaft; process=cut/face + collars</t>
+          <t xml:space="preserve">FM-GR/GA SP-DA/AX/RL/SH plus donor motion tach left/right limits and PPR-C08..10</t>
         </is>
       </c>
       <c r="I143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=Ø8 h6 =7.991-8.000 x28; metal collars; one pivot and one end roller axle; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope</t>
         </is>
       </c>
       <c r="J143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K143" t="inlineStr" s="0">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="M143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="N143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-AX-01.pdf</t>
+          <t xml:space="preserve">docs/drawings/v0.8/SP-001_spooler_traverse.svg</t>
         </is>
       </c>
       <c r="O143" t="inlineStr" s="0">
@@ -12506,19 +12506,19 @@
       </c>
       <c r="Q143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=mixed; cash_class=MIXED; status=DESIGNED; quantity_unit=each; 1 kg spool; A15 spool tach and A5/A6 limits; radius remains geometry/wound-length estimate with uncertainty</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-BP-01</t>
+          <t xml:space="preserve">SP-AW-08</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool 6001 bearing pocket plate</t>
+          <t xml:space="preserve">Dancer thrust shim washers</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="0">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="E144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="0">
@@ -12543,22 +12543,22 @@
       </c>
       <c r="G144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">10 mm 6061-T6; process=waterjet rough + pocket bore finish</t>
+          <t xml:space="preserve">304 stainless; process=precision shim cut + deburr</t>
         </is>
       </c>
       <c r="I144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=105 x10 x60; bearing centre X30/Z30; Ø28.000–28.021 H7 x8.05–8.10 pocket from marked inner face; Ø26 through relief leaves 1.95–2.00 shoulder; 4xØ5.5 retainer + 2xØ5.5 profile tab; matched axis position ±0.05; datum=A=frame mounting face; B=primary bearing axis; C=secondary bearing/fastener axis; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=OD16 +/-0.10; ID8.20 +0.10/0; thickness0.50 +/-0.03; burr free; select/shim for assembled endplay0.10-0.30; 2 pivot and 3 roller stack; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K144" t="inlineStr" s="0">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="N144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-BP-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-AW-08.pdf</t>
         </is>
       </c>
       <c r="O144" t="inlineStr" s="0">
@@ -12593,19 +12593,19 @@
       </c>
       <c r="Q144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=MAKE; cash_class=CASH; status=FABRICATION_HOLD; quantity_unit=each; SP-01 subpart; nominal assembly geometry only; measure endplay0.10-0.30; no cutting or energization authorization; MATCHED_DETAIL_NOT_ADDITIONAL_QUANTITY: SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-BR-01</t>
+          <t xml:space="preserve">SP-AX-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool 6001 outer-ring retainer</t>
+          <t xml:space="preserve">Dancer pivot axle</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="0">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="E145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="0">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="G145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2 mm 304 stainless sheet; process=laser cut + deburr</t>
+          <t xml:space="preserve">8 h6 stainless ground shaft; process=cut + face + deburr</t>
         </is>
       </c>
       <c r="I145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=54 x2 x54; Ø26.0 +0.10/0 relief gives 0.95–1.00 radial outer-ring overlap; 4xØ5.5 at 44 mm square; flatness0.10; burr away from bearing; use 4x M5 with SP-BP-01; datum=A=frame mounting face; B=primary bearing axis; C=secondary bearing/fastener axis; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=Diameter 7.991-8.000; length 38 +/-0.10; ends C0.2; shaft straightness &lt;=0.05; retain with two SP-SC-08 collars; endplay 0.10-0.30 after adjustment; collar torque and axial slip proof HOLD; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K145" t="inlineStr" s="0">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="N145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-BR-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-AX-01.pdf</t>
         </is>
       </c>
       <c r="O145" t="inlineStr" s="0">
@@ -12680,19 +12680,19 @@
       </c>
       <c r="Q145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=MAKE; cash_class=CASH; status=FABRICATION_HOLD; quantity_unit=each; SP-01 subpart; nominal assembly geometry only; measure endplay0.10-0.30; no cutting or energization authorization; MATCHED_DETAIL_NOT_ADDITIONAL_QUANTITY: SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-DA-01</t>
+          <t xml:space="preserve">SP-AX-02</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer arm</t>
+          <t xml:space="preserve">Dancer end roller axle</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="0">
@@ -12717,22 +12717,22 @@
       </c>
       <c r="G146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
+          <t xml:space="preserve">8 h6 stainless ground shaft; process=cut + face + deburr</t>
         </is>
       </c>
       <c r="I146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=100 mm pivot centres; 12 mm arm; 2xØ8.20 +0.05/0; edge R2; full -25..+25deg motion; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=Diameter 7.991-8.000; length 52 +/-0.10; ends C0.2; shaft straightness &lt;=0.05; retain with two SP-SC-08 collars; endplay 0.10-0.30 after adjustment; collar torque and axial slip proof HOLD; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
       <c r="K146" t="inlineStr" s="0">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="N146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-DA-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-AX-02.pdf</t>
         </is>
       </c>
       <c r="O146" t="inlineStr" s="0">
@@ -12767,19 +12767,19 @@
       </c>
       <c r="Q146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=MAKE; cash_class=CASH; status=FABRICATION_HOLD; quantity_unit=each; SP-01 subpart; nominal assembly geometry only; measure endplay0.10-0.30; no cutting or energization authorization; MATCHED_DETAIL_NOT_ADDITIONAL_QUANTITY: SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-DS-01</t>
+          <t xml:space="preserve">SP-BP-01</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer pivot support plate</t>
+          <t xml:space="preserve">Spool 6001 bearing pocket plate</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="0">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="E147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="0">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
+          <t xml:space="preserve">10 mm 6061-T6; process=waterjet rough + pocket bore finish</t>
         </is>
       </c>
       <c r="I147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=36 x8 x80; pivot Ø8.20 +0.05/0 at X18/Z45; 2xØ5.5 foot mounts; metal support carries spring/tension load; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=105 x10 x60; bearing centre X30/Z30; Ø28.000–28.021 H7 x8.05–8.10 pocket from marked inner face; Ø26 through relief leaves 1.95–2.00 shoulder; 4xØ5.5 retainer + 2xØ5.5 profile tab; matched axis position ±0.05; datum=A=frame mounting face; B=primary bearing axis; C=secondary bearing/fastener axis; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J147" t="inlineStr" s="0">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="N147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-DS-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-BP-01.pdf</t>
         </is>
       </c>
       <c r="O147" t="inlineStr" s="0">
@@ -12861,12 +12861,12 @@
     <row r="148">
       <c r="A148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-MM-01</t>
+          <t xml:space="preserve">SP-BR-01</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Universal NEMA17-class spool motor plate</t>
+          <t xml:space="preserve">Spool 6001 outer-ring retainer</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="0">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="E148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="0">
@@ -12896,12 +12896,12 @@
       </c>
       <c r="H148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm 6061-T6; process=laser/waterjet + drill</t>
+          <t xml:space="preserve">2 mm 304 stainless sheet; process=laser cut + deburr</t>
         </is>
       </c>
       <c r="I148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=101 x6 x52; motor centre X26, Ø24; 4xØ4.5 at 31 mm square; 2xØ5.5 profile tab; actual donor shaft and body measurement required before coupling release; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=54 x2 x54; Ø26.0 +0.10/0 relief gives 0.95–1.00 radial outer-ring overlap; 4xØ5.5 at 44 mm square; flatness0.10; burr away from bearing; use 4x M5 with SP-BP-01; datum=A=frame mounting face; B=primary bearing axis; C=secondary bearing/fastener axis; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J148" t="inlineStr" s="0">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="N148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-MM-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-BR-01.pdf</t>
         </is>
       </c>
       <c r="O148" t="inlineStr" s="0">
@@ -12948,12 +12948,12 @@
     <row r="149">
       <c r="A149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-RL-01</t>
+          <t xml:space="preserve">SP-DA-01</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer end roller</t>
+          <t xml:space="preserve">Dancer arm</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="0">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="H149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">POM-C; process=turn + bore</t>
+          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
         </is>
       </c>
       <c r="I149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=OD20 x20; bore Ø8.20 +0.05/0; diametral axle clearance0.20-0.259; free rotation under 0.2-1.0 N filament tension; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=100 mm pivot centres; 12 mm arm; 2xØ8.20 +0.05/0; edge R2; full -25..+25deg motion; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J149" t="inlineStr" s="0">
@@ -13013,7 +13013,7 @@
       </c>
       <c r="N149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-RL-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-DA-01.pdf</t>
         </is>
       </c>
       <c r="O149" t="inlineStr" s="0">
@@ -13035,12 +13035,12 @@
     <row r="150">
       <c r="A150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-SH-01</t>
+          <t xml:space="preserve">SP-DS-01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool spindle</t>
+          <t xml:space="preserve">Dancer pivot support plate</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="0">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="H150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Ø12 h6 S45C; process=cut/turn faces + collar flats</t>
+          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
         </is>
       </c>
       <c r="I150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=Ø12 h6=11.989-12.000 x143; straightness0.05; two SKF6001-2RSH bore11.992-12.000; axial collars carry spool load; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=36 x8 x80; pivot Ø8.20 +0.05/0 at X18/Z45; 2xØ5.5 foot mounts; metal support carries spring/tension load; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J150" t="inlineStr" s="0">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="N150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-SH-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-DS-01.pdf</t>
         </is>
       </c>
       <c r="O150" t="inlineStr" s="0">
@@ -13122,12 +13122,12 @@
     <row r="151">
       <c r="A151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-TR-01</t>
+          <t xml:space="preserve">SP-MM-01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Traverse rod end plate</t>
+          <t xml:space="preserve">Universal NEMA17-class spool motor plate</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="0">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="E151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="0">
@@ -13157,12 +13157,12 @@
       </c>
       <c r="H151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">5 mm 6061-T6; process=waterjet + ream</t>
+          <t xml:space="preserve">6 mm 6061-T6; process=laser/waterjet + drill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=5 x50 x40; two finished Ø8.20–8.30 at 25 mm spacing; 2xØ5.5 mount; use two Ø8 h6=7.991–8.000 x160 ground steel rods; match-ream pair and accept rod parallelism &lt;=0.10/160; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=101 x6 x52; motor centre X26, Ø24; 4xØ4.5 at 31 mm square; 2xØ5.5 profile tab; actual donor shaft and body measurement required before coupling release; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J151" t="inlineStr" s="0">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="N151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-TR-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-MM-01.pdf</t>
         </is>
       </c>
       <c r="O151" t="inlineStr" s="0">
@@ -13209,12 +13209,12 @@
     <row r="152">
       <c r="A152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-BH-01</t>
+          <t xml:space="preserve">SP-RL-01</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Custom barrel mica band heater</t>
+          <t xml:space="preserve">Dancer end roller</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="0">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="D152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">THERMAL</t>
+          <t xml:space="preserve">SPOOLER</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="0">
@@ -13239,22 +13239,22 @@
       </c>
       <c r="G152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="H152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">mica/NiCr/stainless sheath; process=custom heater RFQ</t>
+          <t xml:space="preserve">POM-C; process=turn + bore</t>
         </is>
       </c>
       <c r="I152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff; drawing tolerance=24 VDC 100 W each; free-state ID34.10–34.20; usable split-closure travel &gt;=1.00; width45 ±0.5; radial build2 nominal; cold resistance 5.76 Ω ±10%; 300 mm fiberglass leads; PE-bonded sheath; PET service 300 C design; no stock Ø35 substitution; datum=A=profile mounting plane; B=barrel axis; C=rear axial datum; verify datum marking on supplier inspection report</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=OD20 x20; bore Ø8.20 +0.05/0; diametral axle clearance0.20-0.259; free rotation under 0.2-1.0 N filament tension; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
         </is>
       </c>
       <c r="K152" t="inlineStr" s="0">
@@ -13274,12 +13274,12 @@
       </c>
       <c r="N152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/final/manufacturing/RFQ/TH-BH-01.pdf</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-RL-01.pdf</t>
         </is>
       </c>
       <c r="O152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P152" t="inlineStr" s="0">
@@ -13289,19 +13289,19 @@
       </c>
       <c r="Q152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-DIE-01</t>
+          <t xml:space="preserve">SP-SC-08</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Die cartridge heater</t>
+          <t xml:space="preserve">Traverse and dancer axle stop collars</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="0">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="D153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">THERMAL</t>
+          <t xml:space="preserve">SPOOLER</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="0">
@@ -13326,17 +13326,17 @@
       </c>
       <c r="G153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="H153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Tempco custom Hi-Density; 321SS sheath; 304SS flange; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">GN 705-8-E reference; bore8 H8 OD16 width8; M4x6 DIN914 included</t>
         </is>
       </c>
       <c r="I153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope</t>
         </is>
       </c>
       <c r="J153" t="inlineStr" s="0">
@@ -13356,17 +13356,17 @@
       </c>
       <c r="M153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
         </is>
       </c>
       <c r="N153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/thermal/parts/TH-DIE-01/drawing_notes.md</t>
+          <t xml:space="preserve">docs/drawings/v0.8/SP-001_spooler_traverse.svg</t>
         </is>
       </c>
       <c r="O153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P153" t="inlineStr" s="0">
@@ -13376,19 +13376,19 @@
       </c>
       <c r="Q153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=PURCHASED_REFERENCE; cash_class=CASH; status=RECEIPT_HOLD; quantity_unit=each; Four traverse + four dancer collars; M4x6 screws included; received tightening torque and axial slip proof HOLD</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-FUSE-01</t>
+          <t xml:space="preserve">SP-SH-01</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Independent one-shot thermal fuse envelope</t>
+          <t xml:space="preserve">Spool spindle</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="0">
@@ -13398,12 +13398,12 @@
       </c>
       <c r="D154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">THERMAL</t>
+          <t xml:space="preserve">SPOOLER</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="0">
@@ -13413,22 +13413,22 @@
       </c>
       <c r="G154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="H154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">300 C-class barrel/die protection; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">Ø12 h6 S45C; process=cut/turn faces + collar flats</t>
         </is>
       </c>
       <c r="I154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=Ø12 h6=11.989-12.000 x143; straightness0.05; two SKF6001-2RSH bore11.992-12.000; axial collars carry spool load; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
         </is>
       </c>
       <c r="K154" t="inlineStr" s="0">
@@ -13443,17 +13443,17 @@
       </c>
       <c r="M154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="N154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/thermal/parts/TH-FUSE-01/drawing_notes.md</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-SH-01.pdf</t>
         </is>
       </c>
       <c r="O154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P154" t="inlineStr" s="0">
@@ -13463,19 +13463,19 @@
       </c>
       <c r="Q154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-INS-01</t>
+          <t xml:space="preserve">SP-TG-01</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PI gold finger polyimide thermal barrier tape, 25 mm x 30 m received roll</t>
+          <t xml:space="preserve">Final traverse guide rods</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="0">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="D155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">THERMAL</t>
+          <t xml:space="preserve">SPOOLER</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="0">
@@ -13505,12 +13505,12 @@
       </c>
       <c r="H155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">polyimide film; listing also states fluororesin release material; adhesive chemistry not specified</t>
+          <t xml:space="preserve">8 h6 ground steel shaft; process=cut/face/deburr; collar witness marks outside carriage stroke</t>
         </is>
       </c>
       <c r="I155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=8 h6 x196; nominal end margin2 beyond each8 mm collar; keep set-screw contact outside carriage path; actual collar torque and shaft retention test HOLD; datum=A=common journal axis; B=drive-end shoulder/face; C=keyway or retaining feature plane; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J155" t="inlineStr" s="0">
@@ -13530,17 +13530,17 @@
       </c>
       <c r="M155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="N155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/drawings/v0.8/EX-003_heater_thermocouple.svg</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-TG-01.pdf</t>
         </is>
       </c>
       <c r="O155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P155" t="inlineStr" s="0">
@@ -13550,19 +13550,19 @@
       </c>
       <c r="Q155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=user stock; cash_class=REUSE_PENDING; status=RECEIPT_TEST_HOLD; quantity_unit=each; received product claim long-term 220-280 C, short-term 300 C; use conservative 220 C continuous design basis; S4/P9 interface peak+U95 &lt;=190 C; no safety function; shield exterior only</t>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=CUT_FROM_VERIFIED_STOCK; cash_class=CASH; status=FABRICATION_HOLD; quantity_unit=each; Part of SP-01; one per TraverseRodA/B; 4x SP-SC-08 collars total; supplier stock dimensions and straightness require receipt inspection; no cutting authorization; MATCHED_DETAIL_NOT_ADDITIONAL_QUANTITY: SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-TC-01</t>
+          <t xml:space="preserve">SP-TR-01</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+          <t xml:space="preserve">Y-axis traverse stepped support</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="0">
@@ -13572,12 +13572,12 @@
       </c>
       <c r="D156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">THERMAL</t>
+          <t xml:space="preserve">SPOOLER</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="0">
@@ -13587,22 +13587,22 @@
       </c>
       <c r="G156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="H156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
         </is>
       </c>
       <c r="I156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+          <t xml:space="preserve">spindle/bearing fit; dancer/traverse envelope; drawing tolerance=8x60x132; stem14x84; rod bores8.20-8.30 at local Y10/35 Z114; M5 holes5.5 at Y7 Z8/32; two SP-TG-01 rods8 h6 x196; four SP-SC-08 collars outside support plates; parallelism&lt;=0.10 over support spacing; spindle-parallel Y axis; four M5x16 plus received washer/T-nut; received collar torque/anti-slip test and bracket/joint proof HOLD; datum=A=frame mounting plane; B=primary edge; C=mounting-hole centreline; verify datum marking on supplier inspection report</t>
         </is>
       </c>
       <c r="J156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+          <t xml:space="preserve">NOT_APPLICABLE—make from released file</t>
         </is>
       </c>
       <c r="K156" t="inlineStr" s="0">
@@ -13617,17 +13617,17 @@
       </c>
       <c r="M156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="N156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">exports/thermal/parts/TH-TC-01/drawing_notes.md</t>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/SP-TR-01.pdf</t>
         </is>
       </c>
       <c r="O156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 17; docs/final/assembly_steps.csv</t>
         </is>
       </c>
       <c r="P156" t="inlineStr" s="0">
@@ -13637,99 +13637,621 @@
       </c>
       <c r="Q156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">TH-BH-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Custom barrel mica band heater Z2/Z3</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">THERMAL</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">mica/NiCr/stainless sheath; process=custom heater RFQ</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff; drawing tolerance=24 VDC 100 W each; free-state ID34.10–34.20; usable split-closure travel &gt;=1.00; width45 ±0.5; radial build2 nominal; cold resistance 5.76 Ω ±10%; 300 mm fiberglass leads; PE-bonded sheath; PET service 300 C design; no stock Ø35 substitution; datum=A=profile mounting plane; B=barrel axis; C=rear axial datum; verify datum marking on supplier inspection report</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/TH-BH-01.pdf</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-BH-02</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Custom barrel mica band heater Z1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">THERMAL</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">mica/NiCr/stainless sheath; process=custom heater RFQ</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff; drawing tolerance=24 VDC 100 W each; free-state ID34.10–34.20; usable split-closure travel &gt;=1.00; width40 ±0.5; radial build2 nominal; cold resistance 5.76 Ω ±10%; 300 mm fiberglass leads; PE-bonded sheath; PET service 300 C design; no stock Ø35 substitution; reduced-width 100 W design requires supplier watt-density and lead-layout review; thermal response NOT_RUN; datum=A=profile mounting plane; B=barrel axis; C=rear axial datum; verify datum marking on supplier inspection report</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">exports/final/manufacturing/RFQ/TH-BH-02.pdf</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval; FINAL MANUFACTURING DETAIL: exports/final/manufacturing/RFQ/manifest.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-DIE-01</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Die cartridge heater</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">THERMAL</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Tempco custom Hi-Density; 321SS sheath; 304SS flange; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">exports/thermal/parts/TH-DIE-01/drawing_notes.md</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-FUSE-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Independent one-shot thermal fuse envelope</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">THERMAL</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">300 C-class barrel/die protection; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">exports/thermal/parts/TH-FUSE-01/drawing_notes.md</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-INS-01</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PI gold finger polyimide thermal barrier tape, 25 mm x 30 m received roll</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">THERMAL</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">MIXED</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">polyimide film; listing also states fluororesin release material; adhesive chemistry not specified</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/drawings/v0.8/EX-003_heater_thermocouple.svg</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">AUTHORITATIVE DESIGN SOURCE: bom/bom.csv; source=user stock; cash_class=REUSE_PENDING; status=RECEIPT_TEST_HOLD; quantity_unit=each; received product claim long-term 220-280 C, short-term 300 C; use conservative 220 C continuous design basis; S4/P9 interface peak+U95 &lt;=190 C; no safety function; shield exterior only</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-TC-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">THERMAL</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">REQUIRED</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">exports/thermal/parts/TH-TC-01/drawing_notes.md</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">TH-TCR-01</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr" s="0">
+      <c r="B163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Thermocouple stop-collar retainer bridge</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr" s="0">
+      <c r="C163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">final-design-fabrication-closure-v0.8</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr" s="0">
+      <c r="D163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">THERMAL</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr" s="0">
+      <c r="E163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr" s="0">
+      <c r="F163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">REQUIRED</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr" s="0">
+      <c r="G163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">BUY_TO_SPEC</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr" s="0">
+      <c r="H163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">304 stainless t1.5; process=buy/custom fabricate to thermal drawing note</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr" s="0">
+      <c r="I163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">heater fit, insulation, branch fuse and independent thermal cutoff</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr" s="0">
+      <c r="J163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NONE_APPROVED—exact make/model and receipt evidence pending</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr" s="0">
+      <c r="K163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NONE_APPROVED—deviation requires interface review and affected recalculation/calibration</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr" s="0">
+      <c r="L163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr" s="0">
+      <c r="M163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr" s="0">
+      <c r="N163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">exports/thermal/parts/TH-TCR-01/drawing_notes.md</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr" s="0">
+      <c r="O163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">docs/final/complete_build_manual_ko.pdf step 13; docs/final/assembly_steps.csv</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr" s="0">
+      <c r="P163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">firmware/arduino_mega/src + released pin map/calibration; physical calibration required</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr" s="0">
+      <c r="Q163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv; parent design authority remains bom/bom.csv; procurement/fabrication requires user approval</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q157"/>
+  <autoFilter ref="A1:Q163"/>
 </worksheet>
 </file>
 
@@ -13804,7 +14326,7 @@
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">M4x10 latch flag screw</t>
+          <t xml:space="preserve">M4x16 90° flat-head latch flag screw + washer + nyloc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="0">
@@ -13819,7 +14341,7 @@
       </c>
       <c r="F2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1x M4 heat-set insert OD4.6 x L5</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="0">
@@ -13829,7 +14351,7 @@
       </c>
       <c r="H2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">M4 insert bore Ø4.6 x5 blind; rail slide gap 0.35; witness mark and no crack</t>
+          <t xml:space="preserve">M4 through bore Ø4.50–4.70 with Ø8.4×2 90° underside countersink; rail slide gap0.35; witness mark and no crack</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="0">
@@ -13881,7 +14403,7 @@
       </c>
       <c r="H3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x Ø4.5 mount; 2x Ø6.6 tie-bolt; 100x50 outlet; staggered 72 mm ledges; witness mark and no crack</t>
+          <t xml:space="preserve">4x Ø4.5 mount; 2x Ø10.5 steel-sleeve clearance; 100x50 outlet; staggered 72 mm ledges; witness mark and no crack</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="0">
@@ -13908,7 +14430,7 @@
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">chamber M6 tie bolts through clearance holes</t>
+          <t xml:space="preserve">chamber M6 tie bolts inside steel sleeves</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="0">
@@ -13933,7 +14455,7 @@
       </c>
       <c r="H4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x Ø4.5 mount; 2x Ø6.6 tie-bolt; 100x50 outlet; staggered 72 mm ledges; witness mark and no crack</t>
+          <t xml:space="preserve">4x Ø4.5 mount; 2x Ø10.5 steel-sleeve clearance; 100x50 outlet; staggered 72 mm ledges; witness mark and no crack</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="0">
@@ -13955,7 +14477,7 @@
       </c>
       <c r="B5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C03 / 1 mm sheet bin and screen rails</t>
+          <t xml:space="preserve">PPR-C03 / 1.00 ±0.05 mm sheet bin and screen rails</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="0">
@@ -14111,12 +14633,12 @@
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C06 / LED/photodiode cross frame and opposite half</t>
+          <t xml:space="preserve">PPR-C06 / LED/photodiode cross frame</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">M3x12</t>
+          <t xml:space="preserve">M3x12 + washers + all-metal nuts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="0">
@@ -14131,7 +14653,7 @@
       </c>
       <c r="F8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x M3 heat-set insert OD4.6 x L5</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="0">
@@ -14141,7 +14663,7 @@
       </c>
       <c r="H8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x Ø4.6 x5 blind insert bores; 8 mm optical slot; witness mark and no crack</t>
+          <t xml:space="preserve">4x Ø3.40–3.50 through bores; 8 mm optical slot; complete-pair functional alignment; witness mark and no crack</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="0">
@@ -14245,7 +14767,7 @@
       </c>
       <c r="H10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2x Ø5.5 base holes; Ø5.2 fixed-axle bore; witness mark and no crack</t>
+          <t xml:space="preserve">2x Ø5.5 base holes; Ø5.20–5.40 fixed-axle bore; complete-pair hand-pass alignment; witness mark and no crack</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="0">
@@ -14267,7 +14789,7 @@
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C09 / 12 mm metal spindle and metal collar</t>
+          <t xml:space="preserve">PPR-C09 / 12 mm metal spindle, metal collar, and received spool</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="0">
@@ -14297,7 +14819,7 @@
       </c>
       <c r="H11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Ø12.2 axial bore; Ø6.6 radial through hole; witness mark and no crack</t>
+          <t xml:space="preserve">Ø12.20–12.40 axial bore; Ø6.6 radial through clamp; metal collar carries axial load; witness mark and no crack</t>
         </is>
       </c>
       <c r="I11" t="inlineStr" s="0">
@@ -14319,12 +14841,12 @@
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C10 / donor rods and GT2 belt</t>
+          <t xml:space="preserve">PPR-C10 / specified Ø8 h6 rods and GT2 belt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">M4x16 belt-clamp screws</t>
+          <t xml:space="preserve">M4x25 belt-clamp screws + washers + nyloc</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="0">
@@ -14339,7 +14861,7 @@
       </c>
       <c r="F12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2x M4 heat-set insert OD5.6 x L6 or through nyloc</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="0">
@@ -14349,7 +14871,7 @@
       </c>
       <c r="H12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2x Ø8.4 rod bores; 2x Ø4.5 clamp bores; witness mark and no crack</t>
+          <t xml:space="preserve">2x Ø8.40–8.50 rod bores; 2x Ø4.50–4.70 through clamp bores; witness mark and no crack</t>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="0">
@@ -14376,7 +14898,7 @@
       </c>
       <c r="C13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">M3x10</t>
+          <t xml:space="preserve">M3x16 + washers + all-metal nuts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="0">
@@ -14391,7 +14913,7 @@
       </c>
       <c r="F13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x M3 heat-set insert OD4.2 x L5</t>
+          <t xml:space="preserve">none</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="0">
@@ -14401,7 +14923,7 @@
       </c>
       <c r="H13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x Ø4.2 x5 blind insert bores; 145x82 display opening; witness mark and no crack</t>
+          <t xml:space="preserve">4x Ø3.40–3.50 through bores; 145x82 display opening; witness mark and no crack</t>
         </is>
       </c>
       <c r="I13" t="inlineStr" s="0">
@@ -14480,7 +15002,7 @@
       </c>
       <c r="C15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">M5x12 SHCS + washer + prevailing T-nut; 56 kits paired across 28 two-fastener corner brackets</t>
+          <t xml:space="preserve">BASE FRAME ALLOWANCE ONLY: M5x12 + washer + T-nut 56 kits; not final GGM joint count; FR-TIE-01 needs four separate M5x10 kits</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="0">
@@ -14505,7 +15027,7 @@
       </c>
       <c r="H15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">all 56 witness marks present; frame diagonal &lt;=1.0 mm</t>
+          <t xml:space="preserve">P2 member-by-member connection review; final GGM bracket/T-nut allocation and tie thread engagement required; frame diagonal &lt;=1.0 mm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr" s="0">
@@ -14515,7 +15037,7 @@
       </c>
       <c r="J15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RELEASED_DIGITAL</t>
+          <t xml:space="preserve">HOLD_GGM_MEMBER_CONNECTION_RECEIPT_REVIEW</t>
         </is>
       </c>
     </row>
@@ -15312,7 +15834,7 @@
       </c>
       <c r="C31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">M3x8 A4-80 SHCS + Schnorr washer</t>
+          <t xml:space="preserve">M3x6 A4-80 SHCS + Schnorr washer; M3x8 prohibited in 4 mm blind threads</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="0">
@@ -15337,7 +15859,7 @@
       </c>
       <c r="H31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">four stop collars captured; 20 N pull causes &lt;=0.10 mm motion cold and after thermal cycle</t>
+          <t xml:space="preserve">confirm actual washer/collar/bridge stack, useful thread engagement and positive bottom clearance before torque; nominal M3x6 clears whereas M3x8 bottoms; four stop collars captured; 20 N pull causes &lt;=0.10 mm motion cold and after thermal cycle</t>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="0">
@@ -15347,7 +15869,7 @@
       </c>
       <c r="J31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">RELEASED_DIGITAL_PHYSICAL_NOT_RUN</t>
+          <t xml:space="preserve">HOLD_RECEIVED_RETAINER_STACK_AND_PULL_TEST</t>
         </is>
       </c>
     </row>
@@ -15417,7 +15939,7 @@
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">0.779</t>
+          <t xml:space="preserve">0.798</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="0">
@@ -19146,7 +19668,7 @@
       </c>
       <c r="B72" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">compact profile frame cut set</t>
+          <t xml:space="preserve">GGM R1 integrated profile cut set</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="0">
@@ -19171,19 +19693,19 @@
       </c>
       <c r="G72" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">20x20 aluminum profile 890x4 430x10 660x6 300x2 318x1 280x2 50x1 plus local 20x40 660x2</t>
+          <t xml:space="preserve">2020: 36 members / 15078 mm; 2040: 4 members / 2180 mm; member-by-member frame_cut_list.csv</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GD-01</t>
+          <t xml:space="preserve">FR-TIE-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">cutter and hot-zone guards</t>
+          <t xml:space="preserve">formed steel bottom frame tie replacing 2020 L430</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="0">
@@ -19208,19 +19730,19 @@
       </c>
       <c r="G73" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">metal sheet plus ABS cold covers</t>
+          <t xml:space="preserve">S275JR; finished U40x20x3 R3 x470; 4xD5.5 at X10/460 Y12/28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_ChainGuard</t>
+          <t xml:space="preserve">GD-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_ChainGuard</t>
+          <t xml:space="preserve">cutter and hot-zone guards</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="0">
@@ -19230,34 +19752,34 @@
       </c>
       <c r="D74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1mm folded steel plus2x20x20 mounting tabs; twoM3 to front bearing plate; interlock required; process=1 mm 강판 절단/절곡 + 두 mounting tab</t>
+          <t xml:space="preserve">metal sheet plus ABS cold covers</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_CouplingGuard</t>
+          <t xml:space="preserve">GGM_ChainGuard</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_CouplingGuard</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_ChainGuard</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="0">
@@ -19282,19 +19804,19 @@
       </c>
       <c r="G75" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=1 mm 강판 롤 + 2 mm half flange</t>
+          <t xml:space="preserve">1mm folded steel plus2x20x20 mounting tabs; twoM3 to front bearing plate; interlock required; process=1 mm 강판 절단/절곡 + 두 mounting tab</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_FuseInput</t>
+          <t xml:space="preserve">GGM_EX_CouplingGuard</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseInput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_CouplingGuard</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="0">
@@ -19319,19 +19841,19 @@
       </c>
       <c r="G76" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
+          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=1 mm 강판 롤 + 2 mm half flange</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_FuseOutput</t>
+          <t xml:space="preserve">GGM_EX_FuseInput</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseOutput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseInput</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="0">
@@ -19363,12 +19885,12 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_FusePinBlank</t>
+          <t xml:space="preserve">GGM_EX_FuseOutput</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FusePinBlank</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FuseOutput</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="0">
@@ -19393,19 +19915,19 @@
       </c>
       <c r="G78" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_MotorKey</t>
+          <t xml:space="preserve">GGM_EX_FusePinBlank</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_MotorKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_FusePinBlank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="0">
@@ -19430,19 +19952,19 @@
       </c>
       <c r="G79" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_Mount</t>
+          <t xml:space="preserve">GGM_EX_MotorKey</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_Mount</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_MotorKey</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="0">
@@ -19467,19 +19989,19 @@
       </c>
       <c r="G80" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm S275 plate; use catalog eccentric output datum; process=판재 절단 + 드릴</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_RadialCap</t>
+          <t xml:space="preserve">GGM_EX_Mount</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialCap</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_Mount</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="0">
@@ -19504,19 +20026,19 @@
       </c>
       <c r="G81" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel t2; ID27.4 outer-ring-only retainer; M3 screws; process=2 mm 판재 절단 + 드릴</t>
+          <t xml:space="preserve">6 mm S275 plate; use catalog eccentric output datum; process=판재 절단 + 드릴</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_RadialHolder</t>
+          <t xml:space="preserve">GGM_EX_RadialCap</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialHolder</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialCap</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="0">
@@ -19541,19 +20063,19 @@
       </c>
       <c r="G82" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275 t10; bore32.03; 4x4.5; matching M4 in thrust plate; process=판재 보링/리머 + 드릴/탭</t>
+          <t xml:space="preserve">steel t2; ID27.4 outer-ring-only retainer; M3 screws; process=2 mm 판재 절단 + 드릴</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_EX_ScrewKey</t>
+          <t xml:space="preserve">GGM_EX_RadialHolder</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_ScrewKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_RadialHolder</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="0">
@@ -19578,19 +20100,19 @@
       </c>
       <c r="G83" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S275 t10; bore32.03; 4x4.5; matching M4 in thrust plate; process=판재 보링/리머 + 드릴/탭</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_front</t>
+          <t xml:space="preserve">GGM_EX_ScrewKey</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_front</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_EX_ScrewKey</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="0">
@@ -19615,19 +20137,19 @@
       </c>
       <c r="G84" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel ID12.1 OD17 shim/spacer; inner ring only; process=강관/washer 선삭</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_pinionfront</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_front</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionfront</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_front</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="0">
@@ -19659,12 +20181,12 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_pinionrear</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_pinionfront</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionrear</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionfront</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="0">
@@ -19696,12 +20218,12 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_JackInnerSpacer_rear</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_pinionrear</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_rear</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_pinionrear</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="0">
@@ -19733,12 +20255,12 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_12T</t>
+          <t xml:space="preserve">GGM_JackInnerSpacer_rear</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ANSI #35 12T steel keyed sprocket</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_JackInnerSpacer_rear</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="0">
@@ -19748,34 +20270,34 @@
       </c>
       <c r="D88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CURRENT GGM PURCHASED SPROCKET SOURCE: control/ggm_drive_contract.json + analysis/drive_acceptance_v08/drive_component_register.csv</t>
+          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CHECK_EXISTING_STOCK_FIRST—PURCHASE_USER_APPROVAL_REQUIRED—PHYSICAL_RECEIPT_HOLD</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY #35 12T steel, hub15, key4.1; GGM_SH_Jackshaft D12 h6; 4x4 steel; key flank carries torque</t>
+          <t xml:space="preserve">steel ID12.1 OD17 shim/spacer; inner ring only; process=강관/washer 선삭</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_30T</t>
+          <t xml:space="preserve">GGM_SH_12T</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ANSI #35 30T steel keyed sprocket</t>
+          <t xml:space="preserve">ANSI #35 12T steel keyed sprocket</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="0">
@@ -19800,19 +20322,19 @@
       </c>
       <c r="G89" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY #35 30T steel, hub28, key6.1; CUT-05R D25 h6 drive-end land; 6x6x20 steel; key flank carries torque</t>
+          <t xml:space="preserve">BUY #35 12T steel, hub15, key4.1; GGM_SH_Jackshaft D12 h6; 4x4 steel; key flank carries torque</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Angle201</t>
+          <t xml:space="preserve">GGM_SH_30T</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle201</t>
+          <t xml:space="preserve">ANSI #35 30T steel keyed sprocket</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="0">
@@ -19822,34 +20344,34 @@
       </c>
       <c r="D90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE</t>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv</t>
+          <t xml:space="preserve">CURRENT GGM PURCHASED SPROCKET SOURCE: control/ggm_drive_contract.json + analysis/drive_acceptance_v08/drive_component_register.csv</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
+          <t xml:space="preserve">CHECK_EXISTING_STOCK_FIRST—PURCHASE_USER_APPROVAL_REQUIRED—PHYSICAL_RECEIPT_HOLD</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S275 stock angle; continuous3mm fillet both legs; jig before welding; process=6 mm 판재 두 조각 + 용접</t>
+          <t xml:space="preserve">BUY #35 30T steel, hub28, key6.1; CUT-05R D25 h6 drive-end land; 6x6x20 steel; key flank carries torque</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Angle83</t>
+          <t xml:space="preserve">GGM_SH_Angle201</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle83</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle201</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="0">
@@ -19881,12 +20403,12 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Base</t>
+          <t xml:space="preserve">GGM_SH_Angle83</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Base</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Angle83</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="0">
@@ -19911,19 +20433,19 @@
       </c>
       <c r="G92" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm S275 sheet; fourM6 base holes plus fourM5 end-tap post holes; process=판재 절단 + 드릴</t>
+          <t xml:space="preserve">S275 stock angle; continuous3mm fillet both legs; jig before welding; process=6 mm 판재 두 조각 + 용접</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap271</t>
+          <t xml:space="preserve">GGM_SH_Base</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap271</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Base</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="0">
@@ -19948,19 +20470,19 @@
       </c>
       <c r="G93" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2 mm steel; M3 retainer screws; process=2 mm 판재 절단 + 드릴</t>
+          <t xml:space="preserve">6 mm S275 sheet; fourM6 base holes plus fourM5 end-tap post holes; process=판재 절단 + 드릴</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap283</t>
+          <t xml:space="preserve">GGM_SH_BearingCap271</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap283</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap271</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="0">
@@ -19992,12 +20514,12 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap301</t>
+          <t xml:space="preserve">GGM_SH_BearingCap283</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap301</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap283</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="0">
@@ -20029,12 +20551,12 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingCap313</t>
+          <t xml:space="preserve">GGM_SH_BearingCap301</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap313</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap301</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="0">
@@ -20066,12 +20588,12 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingPlate273</t>
+          <t xml:space="preserve">GGM_SH_BearingCap313</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate273</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingCap313</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="0">
@@ -20096,19 +20618,19 @@
       </c>
       <c r="G97" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">216x60x10 plate,32.03 bore,193x40 asymmetric hole grid; rings retained by caps; process=판재 + 보링/리머 + 탭</t>
+          <t xml:space="preserve">2 mm steel; M3 retainer screws; process=2 mm 판재 절단 + 드릴</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_BearingPlate303</t>
+          <t xml:space="preserve">GGM_SH_BearingPlate273</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate303</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate273</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="0">
@@ -20140,12 +20662,12 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_CouplingGuard</t>
+          <t xml:space="preserve">GGM_SH_BearingPlate303</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CouplingGuard</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_BearingPlate303</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="0">
@@ -20170,19 +20692,19 @@
       </c>
       <c r="G99" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=2 mm 강판 롤 + 분할 seam</t>
+          <t xml:space="preserve">216x60x10 plate,32.03 bore,193x40 asymmetric hole grid; rings retained by caps; process=판재 + 보링/리머 + 탭</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_CutterKey</t>
+          <t xml:space="preserve">GGM_SH_CouplingGuard</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CutterKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CouplingGuard</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="0">
@@ -20207,19 +20729,19 @@
       </c>
       <c r="G100" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6x6x20 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">split metal cover: 2 formed halves, OD76x2 front flange, fourM3 mounts, 1mm seam; process=2 mm 강판 롤 + 분할 seam</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_FuseInput</t>
+          <t xml:space="preserve">GGM_SH_CutterKey</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseInput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_CutterKey</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="0">
@@ -20244,19 +20766,19 @@
       </c>
       <c r="G101" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
+          <t xml:space="preserve">6x6x20 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_FuseOutput</t>
+          <t xml:space="preserve">GGM_SH_FuseInput</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseOutput</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseInput</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="0">
@@ -20288,12 +20810,12 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_FusePinBlank</t>
+          <t xml:space="preserve">GGM_SH_FuseOutput</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FusePinBlank</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FuseOutput</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="0">
@@ -20318,19 +20840,19 @@
       </c>
       <c r="G103" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=선삭 + 키홈 + 드릴/탭</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_JackInputKey</t>
+          <t xml:space="preserve">GGM_SH_FusePinBlank</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackInputKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_FusePinBlank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="0">
@@ -20355,19 +20877,19 @@
       </c>
       <c r="G104" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S45C hubs / brass uncalibrated pin blank; release target8.8-9.3Nm; process=황동봉 선삭 + 교차 드릴</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_JackSprocketKey</t>
+          <t xml:space="preserve">GGM_SH_JackInputKey</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackSprocketKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackInputKey</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="0">
@@ -20399,12 +20921,12 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Jackshaft</t>
+          <t xml:space="preserve">GGM_SH_JackSprocketKey</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Jackshaft</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_JackSprocketKey</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="0">
@@ -20429,19 +20951,19 @@
       </c>
       <c r="G106" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">S45C 12 h6 x78; two 4 mm keys; process=규격 S45C 봉 + 선삭 + 키홈</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_MotorKey</t>
+          <t xml:space="preserve">GGM_SH_Jackshaft</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_MotorKey</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Jackshaft</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="0">
@@ -20466,19 +20988,19 @@
       </c>
       <c r="G107" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
+          <t xml:space="preserve">S45C 12 h6 x78; two 4 mm keys; process=규격 S45C 봉 + 선삭 + 키홈</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Mount</t>
+          <t xml:space="preserve">GGM_SH_MotorKey</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Mount</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_MotorKey</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="0">
@@ -20503,19 +21025,19 @@
       </c>
       <c r="G108" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm S275 plate; 4x6.6 PCD104; pilot36.5; process=판재 절단 + 드릴 + 지그 용접</t>
+          <t xml:space="preserve">4x4 steel key; process=규격 키 stock 절단</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_220_100</t>
+          <t xml:space="preserve">GGM_SH_Mount</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_100</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Mount</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="0">
@@ -20540,19 +21062,19 @@
       </c>
       <c r="G109" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel spacer 12/6.6 x10; process=규격 강관 절단 + 끝면 다듬기</t>
+          <t xml:space="preserve">6 mm S275 plate; 4x6.6 PCD104; pilot36.5; process=판재 절단 + 드릴 + 지그 용접</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_220_280</t>
+          <t xml:space="preserve">GGM_SH_Spacer_220_100</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_280</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_100</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="0">
@@ -20584,12 +21106,12 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_90_100</t>
+          <t xml:space="preserve">GGM_SH_Spacer_220_280</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_100</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_220_280</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="0">
@@ -20621,12 +21143,12 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM_SH_Spacer_90_280</t>
+          <t xml:space="preserve">GGM_SH_Spacer_90_100</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_280</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_100</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="0">
@@ -20658,12 +21180,12 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">HP-01</t>
+          <t xml:space="preserve">GGM_SH_Spacer_90_280</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">refillable sliding-lid hopper</t>
+          <t xml:space="preserve">GGM drive manufactured part: GGM_SH_Spacer_90_280</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="0">
@@ -20673,34 +21195,34 @@
       </c>
       <c r="D113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">MAKE</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">bom/bom.csv</t>
+          <t xml:space="preserve">authoritative sub-manifest: exports/final/manufacturing/drive_ggm/manifest.csv</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PHYSICAL_NOT_RUN</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IN-HOP-01 plus PPR-C01/C02</t>
+          <t xml:space="preserve">steel spacer 12/6.6 x10; process=규격 강관 절단 + 끝면 다듬기</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">IN-HOP-01</t>
+          <t xml:space="preserve">HP-01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Refillable input hopper</t>
+          <t xml:space="preserve">refillable sliding-lid hopper</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="0">
@@ -20710,34 +21232,34 @@
       </c>
       <c r="D114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2 mm 5052-H32 aluminum; process=roll cone/cylinder + TIG weld + deburr</t>
+          <t xml:space="preserve">IN-HOP-01 plus PPR-C01/C02</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PL-01</t>
+          <t xml:space="preserve">IN-HOP-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">puller pair with tach</t>
+          <t xml:space="preserve">Refillable input hopper</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="0">
@@ -20747,34 +21269,34 @@
       </c>
       <c r="D115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">bom/bom.csv</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_INVENTORY_VERIFICATION_REQUIRED</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">FM-PL-01/RL-01/AX-01 plus donor motor and tach</t>
+          <t xml:space="preserve">2 mm 5052-H32 aluminum; process=roll cone/cylinder + TIG weld + deburr</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C01</t>
+          <t xml:space="preserve">PL-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Sliding hopper lid</t>
+          <t xml:space="preserve">puller pair with tach</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="0">
@@ -20784,34 +21306,34 @@
       </c>
       <c r="D116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_3D_PRINT</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/print/print_manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PRINT_PACKAGE_PASS</t>
+          <t xml:space="preserve">USER_INVENTORY_VERIFICATION_REQUIRED</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 20% infill</t>
+          <t xml:space="preserve">FM-PL-01/RL-01/AX-01 plus donor motor and tach</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C02</t>
+          <t xml:space="preserve">PPR-C01</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Anti-reach baffle chute</t>
+          <t xml:space="preserve">Sliding hopper lid</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="0">
@@ -20836,24 +21358,24 @@
       </c>
       <c r="G117" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 25% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 20% infill</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C03</t>
+          <t xml:space="preserve">PPR-C02</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Flake bin sheet corner</t>
+          <t xml:space="preserve">Anti-reach baffle chute</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="0">
@@ -20873,24 +21395,24 @@
       </c>
       <c r="G118" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.28 mm; 4 walls; 25% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 25% infill</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C04</t>
+          <t xml:space="preserve">PPR-C03</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Screen drawer handle</t>
+          <t xml:space="preserve">Flake bin sheet corner</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="0">
@@ -20910,24 +21432,24 @@
       </c>
       <c r="G119" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 35% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.28 mm; 4 walls; 25% infill</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C05</t>
+          <t xml:space="preserve">PPR-C04</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Cooling duct segment</t>
+          <t xml:space="preserve">Screen drawer handle</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="0">
@@ -20947,19 +21469,19 @@
       </c>
       <c r="G120" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 15% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 35% infill</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C06</t>
+          <t xml:space="preserve">PPR-C05</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Gauge enclosure half</t>
+          <t xml:space="preserve">Cooling duct segment</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="0">
@@ -20984,24 +21506,24 @@
       </c>
       <c r="G121" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 25% infill</t>
+          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 4 walls; 15% infill</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C07</t>
+          <t xml:space="preserve">PPR-C06</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Puller pinch guard</t>
+          <t xml:space="preserve">Gauge enclosure</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="0">
@@ -21021,24 +21543,24 @@
       </c>
       <c r="G122" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 20% infill</t>
+          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 25% infill</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C08</t>
+          <t xml:space="preserve">PPR-C07</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Solid-strand guide axle bracket</t>
+          <t xml:space="preserve">Puller pinch guard</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="0">
@@ -21058,19 +21580,19 @@
       </c>
       <c r="G123" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
+          <t xml:space="preserve">ABS; process=FDM; 0.4 mm nozzle; 0.24 mm; 5 walls; 20% infill</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C09</t>
+          <t xml:space="preserve">PPR-C08</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool cone adapter</t>
+          <t xml:space="preserve">Solid-strand guide axle bracket</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="0">
@@ -21095,24 +21617,24 @@
       </c>
       <c r="G124" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 35% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C10</t>
+          <t xml:space="preserve">PPR-C09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Traverse carriage</t>
+          <t xml:space="preserve">Spool cone adapter</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="0">
@@ -21132,19 +21654,19 @@
       </c>
       <c r="G125" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 35% infill</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C11</t>
+          <t xml:space="preserve">PPR-C10</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Control panel bezel</t>
+          <t xml:space="preserve">Traverse carriage</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="0">
@@ -21169,24 +21691,24 @@
       </c>
       <c r="G126" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 20% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 5 walls; 40% infill</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-C12</t>
+          <t xml:space="preserve">PPR-C11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Cable duct clamp</t>
+          <t xml:space="preserve">Control panel bezel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="0">
@@ -21206,56 +21728,56 @@
       </c>
       <c r="G127" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 50% infill</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 20% infill</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-EXTRUDER-ASM</t>
+          <t xml:space="preserve">PPR-C12</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-EXTRUDER-ASM</t>
+          <t xml:space="preserve">Cable duct clamp</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">REFERENCE_ONLY</t>
+          <t xml:space="preserve">MAKE_3D_PRINT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">active_part_set reference</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/print/print_manifest.csv</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">NOT_APPLICABLE_REFERENCE</t>
+          <t xml:space="preserve">PRINT_PACKAGE_PASS</t>
         </is>
       </c>
       <c r="G128" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference only; exclude from order</t>
+          <t xml:space="preserve">PLA; process=FDM; 0.4 mm nozzle; 0.20 mm; 4 walls; 50% infill</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FEEDER-ASM</t>
+          <t xml:space="preserve">PPR-EXTRUDER-ASM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FEEDER-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-EXTRUDER-ASM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="0">
@@ -21287,12 +21809,12 @@
     <row r="130">
       <c r="A130" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FORMING-ASM</t>
+          <t xml:space="preserve">PPR-FEEDER-ASM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FORMING-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FEEDER-ASM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="0">
@@ -21324,12 +21846,12 @@
     <row r="131">
       <c r="A131" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FRAME-ASM</t>
+          <t xml:space="preserve">PPR-FORMING-ASM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FRAME-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FORMING-ASM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="0">
@@ -21361,12 +21883,12 @@
     <row r="132">
       <c r="A132" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-FULL-ASM</t>
+          <t xml:space="preserve">PPR-FRAME-ASM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-FULL-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FRAME-ASM</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="0">
@@ -21398,12 +21920,12 @@
     <row r="133">
       <c r="A133" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PPR-SHREDDER-ASM</t>
+          <t xml:space="preserve">PPR-FULL-ASM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">reference alias: PPR-SHREDDER-ASM</t>
+          <t xml:space="preserve">reference alias: PPR-FULL-ASM</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="0">
@@ -21435,12 +21957,12 @@
     <row r="134">
       <c r="A134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SF-01</t>
+          <t xml:space="preserve">PPR-SHREDDER-ASM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">latching E-stop and hardwired cut</t>
+          <t xml:space="preserve">reference alias: PPR-SHREDDER-ASM</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="0">
@@ -21450,39 +21972,39 @@
       </c>
       <c r="D134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">REFERENCE_ONLY</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">bom/bom.csv</t>
+          <t xml:space="preserve">active_part_set reference</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
+          <t xml:space="preserve">NOT_APPLICABLE_REFERENCE</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">qualified switch plus relay topology</t>
+          <t xml:space="preserve">reference only; exclude from order</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SF-02</t>
+          <t xml:space="preserve">SF-01</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">lid and service interlocks</t>
+          <t xml:space="preserve">latching E-stop and hardwired cut</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="0">
@@ -21502,24 +22024,24 @@
       </c>
       <c r="G135" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">positive opening switch candidate</t>
+          <t xml:space="preserve">qualified switch plus relay topology</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SF-03</t>
+          <t xml:space="preserve">SF-02</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">thermal and branch fuses</t>
+          <t xml:space="preserve">lid and service interlocks</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="0">
@@ -21539,19 +22061,19 @@
       </c>
       <c r="G136" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">temperature/current rated</t>
+          <t xml:space="preserve">positive opening switch candidate</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-01</t>
+          <t xml:space="preserve">SF-03</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">dual-shaft hook cutter assembly</t>
+          <t xml:space="preserve">thermal and branch fuses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="0">
@@ -21561,7 +22083,7 @@
       </c>
       <c r="D137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_CNC</t>
+          <t xml:space="preserve">BUY</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="0">
@@ -21576,19 +22098,19 @@
       </c>
       <c r="G137" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">steel</t>
+          <t xml:space="preserve">temperature/current rated</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-02</t>
+          <t xml:space="preserve">SH-01</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">removable 5 mm screen</t>
+          <t xml:space="preserve">dual-shaft hook cutter assembly</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="0">
@@ -21613,19 +22135,19 @@
       </c>
       <c r="G138" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">stainless steel</t>
+          <t xml:space="preserve">steel</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-03</t>
+          <t xml:space="preserve">SH-02</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">interchangeable shredder geared DC drive</t>
+          <t xml:space="preserve">removable 5 mm screen</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="0">
@@ -21635,7 +22157,7 @@
       </c>
       <c r="D139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY</t>
+          <t xml:space="preserve">MAKE_CNC</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="0">
@@ -21650,19 +22172,19 @@
       </c>
       <c r="G139" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">GGM K9DG60N2 24V + K9G75C + GGM drive r2 support/jackshaft; existing #35 12T:30T</t>
+          <t xml:space="preserve">stainless steel</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-04</t>
+          <t xml:space="preserve">SH-03</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">interchangeable chain and phase drive</t>
+          <t xml:space="preserve">interchangeable shredder geared DC drive</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="0">
@@ -21672,7 +22194,7 @@
       </c>
       <c r="D140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">BUY</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="0">
@@ -21682,24 +22204,24 @@
       </c>
       <c r="F140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
+          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">direct-keyed GGM_SH_12T/GGM_SH_30T #35 sprockets + DRV-03/03R phase pair + GGM 12 mm jackshaft chain path</t>
+          <t xml:space="preserve">GGM K9DG60N2 24V + K9G75C + GGM drive r2 support/jackshaft; existing #35 12T:30T</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SH-05</t>
+          <t xml:space="preserve">SH-04</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">bidirectional motor driver/current feedback</t>
+          <t xml:space="preserve">interchangeable chain and phase drive</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="0">
@@ -21709,7 +22231,7 @@
       </c>
       <c r="D141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">VERIFY_REUSE_OR_BUY</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="0">
@@ -21719,24 +22241,24 @@
       </c>
       <c r="F141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">owned BTS7960 module + external motor-lead current sensor</t>
+          <t xml:space="preserve">direct-keyed GGM_SH_12T/GGM_SH_30T #35 sprockets + DRV-03/03R phase pair + GGM 12 mm jackshaft chain path</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-01</t>
+          <t xml:space="preserve">SH-05</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">dancer traverse spooler</t>
+          <t xml:space="preserve">bidirectional motor driver/current feedback</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="0">
@@ -21746,7 +22268,7 @@
       </c>
       <c r="D142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MIXED</t>
+          <t xml:space="preserve">VERIFY_REUSE_OR_BUY</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="0">
@@ -21756,76 +22278,76 @@
       </c>
       <c r="F142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
+          <t xml:space="preserve">SUPPLIER_OR_INVENTORY_VERIFICATION_REQUIRED</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">FM-GR/GA SP-DA/AX/RL/SH plus donor motion tach left/right limits and PPR-C08..10</t>
+          <t xml:space="preserve">owned BTS7960 module + external motor-lead current sensor</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-AX-01</t>
+          <t xml:space="preserve">SP-01</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer pivot/roller axles</t>
+          <t xml:space="preserve">dancer traverse spooler</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+          <t xml:space="preserve">SPECIFICATION_RELEASED—PROCUREMENT_NOT_APPROVED</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Ø8 h6 stainless shaft; process=cut/face + collars</t>
+          <t xml:space="preserve">FM-GR/GA SP-DA/AX/RL/SH plus donor motion tach left/right limits and PPR-C08..10</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-BP-01</t>
+          <t xml:space="preserve">SP-AW-08</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool 6001 bearing pocket plate</t>
+          <t xml:space="preserve">Dancer thrust shim washers</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="0">
@@ -21835,34 +22357,34 @@
       </c>
       <c r="G144" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">10 mm 6061-T6; process=waterjet rough + pocket bore finish</t>
+          <t xml:space="preserve">304 stainless; process=precision shim cut + deburr</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-BR-01</t>
+          <t xml:space="preserve">SP-AX-01</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool 6001 outer-ring retainer</t>
+          <t xml:space="preserve">Dancer pivot axle</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="0">
@@ -21872,19 +22394,19 @@
       </c>
       <c r="G145" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2 mm 304 stainless sheet; process=laser cut + deburr</t>
+          <t xml:space="preserve">8 h6 stainless ground shaft; process=cut + face + deburr</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-DA-01</t>
+          <t xml:space="preserve">SP-AX-02</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer arm</t>
+          <t xml:space="preserve">Dancer end roller axle</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="0">
@@ -21894,12 +22416,12 @@
       </c>
       <c r="D146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">MAKE_TO_DRAWING</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="0">
@@ -21909,24 +22431,24 @@
       </c>
       <c r="G146" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
+          <t xml:space="preserve">8 h6 stainless ground shaft; process=cut + face + deburr</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-DS-01</t>
+          <t xml:space="preserve">SP-BP-01</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer pivot support plate</t>
+          <t xml:space="preserve">Spool 6001 bearing pocket plate</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="0">
@@ -21946,24 +22468,24 @@
       </c>
       <c r="G147" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
+          <t xml:space="preserve">10 mm 6061-T6; process=waterjet rough + pocket bore finish</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-MM-01</t>
+          <t xml:space="preserve">SP-BR-01</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Universal NEMA17-class spool motor plate</t>
+          <t xml:space="preserve">Spool 6001 outer-ring retainer</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="0">
@@ -21983,19 +22505,19 @@
       </c>
       <c r="G148" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">6 mm 6061-T6; process=laser/waterjet + drill</t>
+          <t xml:space="preserve">2 mm 304 stainless sheet; process=laser cut + deburr</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-RL-01</t>
+          <t xml:space="preserve">SP-DA-01</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Dancer end roller</t>
+          <t xml:space="preserve">Dancer arm</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="0">
@@ -22020,19 +22542,19 @@
       </c>
       <c r="G149" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">POM-C; process=turn + bore</t>
+          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-SH-01</t>
+          <t xml:space="preserve">SP-DS-01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Spool spindle</t>
+          <t xml:space="preserve">Dancer pivot support plate</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="0">
@@ -22057,24 +22579,24 @@
       </c>
       <c r="G150" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Ø12 h6 S45C; process=cut/turn faces + collar flats</t>
+          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SP-TR-01</t>
+          <t xml:space="preserve">SP-MM-01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Traverse rod end plate</t>
+          <t xml:space="preserve">Universal NEMA17-class spool motor plate</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="0">
@@ -22094,34 +22616,34 @@
       </c>
       <c r="G151" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">5 mm 6061-T6; process=waterjet + ream</t>
+          <t xml:space="preserve">6 mm 6061-T6; process=laser/waterjet + drill</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-BH-01</t>
+          <t xml:space="preserve">SP-RL-01</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Custom barrel mica band heater</t>
+          <t xml:space="preserve">Dancer end roller</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="0">
@@ -22131,98 +22653,98 @@
       </c>
       <c r="G152" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">mica/NiCr/stainless sheath; process=custom heater RFQ</t>
+          <t xml:space="preserve">POM-C; process=turn + bore</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-DIE-01</t>
+          <t xml:space="preserve">SP-SC-08</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Die cartridge heater</t>
+          <t xml:space="preserve">Traverse and dancer axle stop collars</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MIXED</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+          <t xml:space="preserve">bom/bom.csv</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Tempco custom Hi-Density; 321SS sheath; 304SS flange; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">GN 705-8-E reference; bore8 H8 OD16 width8; M4x6 DIN914 included</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-FUSE-01</t>
+          <t xml:space="preserve">SP-SH-01</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Independent one-shot thermal fuse envelope</t>
+          <t xml:space="preserve">Spool spindle</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">300 C-class barrel/die protection; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">Ø12 h6 S45C; process=cut/turn faces + collar flats</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-INS-01</t>
+          <t xml:space="preserve">SP-TG-01</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">PI gold finger polyimide thermal barrier tape, 25 mm x 30 m received roll</t>
+          <t xml:space="preserve">Final traverse guide rods</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="0">
@@ -22237,90 +22759,312 @@
       </c>
       <c r="F155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">polyimide film; listing also states fluororesin release material; adhesive chemistry not specified</t>
+          <t xml:space="preserve">8 h6 ground steel shaft; process=cut/face/deburr; collar witness marks outside carriage stroke</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">TH-TC-01</t>
+          <t xml:space="preserve">SP-TR-01</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+          <t xml:space="preserve">Y-axis traverse stepped support</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">BUY_TO_SPEC</t>
+          <t xml:space="preserve">MAKE_TO_DRAWING</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/fabrication/machine_manifest.csv</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+          <t xml:space="preserve">8 mm 6061-T6; process=waterjet + ream</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">TH-BH-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Custom barrel mica band heater Z2/Z3</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">mica/NiCr/stainless sheath; process=custom heater RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-BH-02</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Custom barrel mica band heater Z1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">DIGITAL_DRAWING_PASS; PART_GATE=PASS; PROCUREMENT_USER_APPROVAL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">mica/NiCr/stainless sheath; process=custom heater RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-DIE-01</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Die cartridge heater</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Tempco custom Hi-Density; 321SS sheath; 304SS flange; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-FUSE-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Independent one-shot thermal fuse envelope</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">300 C-class barrel/die protection; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-INS-01</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PI gold finger polyimide thermal barrier tape, 25 mm x 30 m received roll</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">MIXED</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">bom/bom.csv</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">CANDIDATE_SELECTED—RECEIPT_TEST_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">polyimide film; listing also states fluororesin release material; adhesive chemistry not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">TH-TC-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Tempco MTA1 custom ungrounded Type-K probes</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BUY_TO_SPEC</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Alloy 600 MI sheath Ø3.00 ±0.03; 96% MgO; supplier-welded 304SS stop collar; process=buy/custom fabricate to thermal drawing note</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">TH-TCR-01</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr" s="0">
+      <c r="B163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Thermocouple stop-collar retainer bridge</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr" s="0">
+      <c r="C163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr" s="0">
+      <c r="D163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">BUY_TO_SPEC</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr" s="0">
+      <c r="E163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">SUBORDINATE DETAIL SOURCE: exports/thermal/manifest.csv</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr" s="0">
+      <c r="F163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">USER_APPROVAL_AND_RECEIPT_TEST_HOLD</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr" s="0">
+      <c r="G163" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">304 stainless t1.5; process=buy/custom fabricate to thermal drawing note</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G157"/>
+  <autoFilter ref="A1:G163"/>
 </worksheet>
 </file>